--- a/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,38 +434,1454 @@
           <t>copiado_formaciones</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4W5t03Zl</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.5939393939394</v>
+      </c>
+      <c r="D2" t="n">
+        <v>183.9142191142191</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.248873348873349</v>
+      </c>
+      <c r="F2" t="n">
+        <v>73.07696192696193</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6264459.013209013</v>
+      </c>
+      <c r="H2" t="n">
+        <v>77.26794871794871</v>
+      </c>
+      <c r="I2" t="n">
+        <v>28.34482758620689</v>
+      </c>
+      <c r="J2" t="n">
+        <v>182.6677115987461</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.476489028213166</v>
+      </c>
+      <c r="L2" t="n">
+        <v>82.77742946708466</v>
+      </c>
+      <c r="M2" t="n">
+        <v>39025078.36990596</v>
+      </c>
+      <c r="N2" t="n">
+        <v>84.54858934169279</v>
+      </c>
+      <c r="O2" t="n">
+        <v>25.92492156034011</v>
+      </c>
+      <c r="P2" t="n">
+        <v>184.0404016885578</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.275653228119292</v>
+      </c>
+      <c r="R2" t="n">
+        <v>69.30452076329905</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3189649.25694592</v>
+      </c>
+      <c r="T2" t="n">
+        <v>73.8567595539202</v>
+      </c>
+      <c r="U2" t="n">
+        <v>27.23916141769887</v>
+      </c>
+      <c r="V2" t="n">
+        <v>182.7759192232438</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.85578975567085</v>
+      </c>
+      <c r="X2" t="n">
+        <v>77.71067894979905</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>18106455.36356892</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>80.43294715809579</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rN4paNle</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>26.42551319648094</v>
+      </c>
+      <c r="J3" t="n">
+        <v>183.1233952427501</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.638937764744216</v>
+      </c>
+      <c r="L3" t="n">
+        <v>76.30768980123818</v>
+      </c>
+      <c r="M3" t="n">
+        <v>12049116.97621375</v>
+      </c>
+      <c r="N3" t="n">
+        <v>79.73929618768327</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>24.42543017472892</v>
+      </c>
+      <c r="V3" t="n">
+        <v>183.2220355150019</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.405190466901547</v>
+      </c>
+      <c r="X3" t="n">
+        <v>73.10272227798175</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>9912293.144884309</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>79.10878374495485</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6Le197C2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>25.88896103896104</v>
+      </c>
+      <c r="D4" t="n">
+        <v>183.9542207792208</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.968506493506494</v>
+      </c>
+      <c r="F4" t="n">
+        <v>80.60324675324675</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35643766.23376624</v>
+      </c>
+      <c r="H4" t="n">
+        <v>84.14350649350649</v>
+      </c>
+      <c r="I4" t="n">
+        <v>26.1506993006993</v>
+      </c>
+      <c r="J4" t="n">
+        <v>186.0377622377623</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.365734265734266</v>
+      </c>
+      <c r="L4" t="n">
+        <v>75.84545454545454</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12132167.83216783</v>
+      </c>
+      <c r="N4" t="n">
+        <v>79.19405594405595</v>
+      </c>
+      <c r="O4" t="n">
+        <v>23.97172401799404</v>
+      </c>
+      <c r="P4" t="n">
+        <v>183.0353403019135</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.434322284207868</v>
+      </c>
+      <c r="R4" t="n">
+        <v>72.81321493575498</v>
+      </c>
+      <c r="S4" t="n">
+        <v>13622612.46019427</v>
+      </c>
+      <c r="T4" t="n">
+        <v>80.96641507255352</v>
+      </c>
+      <c r="U4" t="n">
+        <v>23.80062300695785</v>
+      </c>
+      <c r="V4" t="n">
+        <v>186.7136566048331</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.135395750554122</v>
+      </c>
+      <c r="X4" t="n">
+        <v>70.3368254231942</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4364854.247060129</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>76.48432854852538</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jPP565dL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>25.24825174825175</v>
+      </c>
+      <c r="D5" t="n">
+        <v>183.6853146853147</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.038461538461539</v>
+      </c>
+      <c r="F5" t="n">
+        <v>72.25174825174825</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4444405.594405595</v>
+      </c>
+      <c r="H5" t="n">
+        <v>76.72027972027971</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25.5525641025641</v>
+      </c>
+      <c r="J5" t="n">
+        <v>183.2024087024087</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.314180264180264</v>
+      </c>
+      <c r="L5" t="n">
+        <v>73.88158508158507</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9056600.62160062</v>
+      </c>
+      <c r="N5" t="n">
+        <v>78.63418803418803</v>
+      </c>
+      <c r="O5" t="n">
+        <v>24.97644022644022</v>
+      </c>
+      <c r="P5" t="n">
+        <v>183.497594179325</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.147562088908243</v>
+      </c>
+      <c r="R5" t="n">
+        <v>69.30581718850951</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3139694.715540869</v>
+      </c>
+      <c r="T5" t="n">
+        <v>74.44231850770312</v>
+      </c>
+      <c r="U5" t="n">
+        <v>25.32603438491399</v>
+      </c>
+      <c r="V5" t="n">
+        <v>182.6861701317387</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.197505084411439</v>
+      </c>
+      <c r="X5" t="n">
+        <v>69.9860697351082</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3316996.139629292</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>75.71339711756099</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>24.41558441558442</v>
+      </c>
+      <c r="D6" t="n">
+        <v>185.2467532467533</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.266233766233767</v>
+      </c>
+      <c r="F6" t="n">
+        <v>75.07792207792207</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11093181.81818182</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80.07467532467533</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24.82867132867133</v>
+      </c>
+      <c r="J6" t="n">
+        <v>186.0636363636363</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.057342657342657</v>
+      </c>
+      <c r="L6" t="n">
+        <v>73.10314685314685</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5359720.279720278</v>
+      </c>
+      <c r="N6" t="n">
+        <v>77.61748251748251</v>
+      </c>
+      <c r="O6" t="n">
+        <v>23.57238459816046</v>
+      </c>
+      <c r="P6" t="n">
+        <v>185.6021287661436</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.179637896312773</v>
+      </c>
+      <c r="R6" t="n">
+        <v>70.17567077080008</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5404430.919808844</v>
+      </c>
+      <c r="T6" t="n">
+        <v>77.19984893048932</v>
+      </c>
+      <c r="U6" t="n">
+        <v>25.46507138872524</v>
+      </c>
+      <c r="V6" t="n">
+        <v>184.0301636042021</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.089346945789254</v>
+      </c>
+      <c r="X6" t="n">
+        <v>70.11500447913909</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2964692.404817405</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>74.96886243386244</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>24.8034965034965</v>
+      </c>
+      <c r="D7" t="n">
+        <v>184.1674825174825</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.139510489510489</v>
+      </c>
+      <c r="F7" t="n">
+        <v>73.02692307692308</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5162534.965034964</v>
+      </c>
+      <c r="H7" t="n">
+        <v>77.31083916083915</v>
+      </c>
+      <c r="I7" t="n">
+        <v>26.87774294670847</v>
+      </c>
+      <c r="J7" t="n">
+        <v>181.9341692789969</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.755485893416928</v>
+      </c>
+      <c r="L7" t="n">
+        <v>80.00940438871473</v>
+      </c>
+      <c r="M7" t="n">
+        <v>32149529.78056427</v>
+      </c>
+      <c r="N7" t="n">
+        <v>82.11285266457681</v>
+      </c>
+      <c r="O7" t="n">
+        <v>24.25122708488093</v>
+      </c>
+      <c r="P7" t="n">
+        <v>184.3228549228549</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.042764998534229</v>
+      </c>
+      <c r="R7" t="n">
+        <v>69.48662100008254</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2802540.783646553</v>
+      </c>
+      <c r="T7" t="n">
+        <v>74.6287192864116</v>
+      </c>
+      <c r="U7" t="n">
+        <v>25.16416795042023</v>
+      </c>
+      <c r="V7" t="n">
+        <v>182.1068209937539</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.521203584679083</v>
+      </c>
+      <c r="X7" t="n">
+        <v>74.39943178082925</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>13114869.07992693</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>78.62138703536162</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>25.8013468013468</v>
+      </c>
+      <c r="D8" t="n">
+        <v>184.6498316498316</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.232323232323233</v>
+      </c>
+      <c r="F8" t="n">
+        <v>72.12794612794613</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3405134.680134681</v>
+      </c>
+      <c r="H8" t="n">
+        <v>75.64309764309765</v>
+      </c>
+      <c r="I8" t="n">
+        <v>27.26118326118326</v>
+      </c>
+      <c r="J8" t="n">
+        <v>183.0731240981241</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.28946608946609</v>
+      </c>
+      <c r="L8" t="n">
+        <v>78.86031746031745</v>
+      </c>
+      <c r="M8" t="n">
+        <v>21180660.17316017</v>
+      </c>
+      <c r="N8" t="n">
+        <v>80.80743145743146</v>
+      </c>
+      <c r="O8" t="n">
+        <v>26.37323376921078</v>
+      </c>
+      <c r="P8" t="n">
+        <v>184.1473743582939</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.169356229126344</v>
+      </c>
+      <c r="R8" t="n">
+        <v>69.79790777549398</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2347848.359601233</v>
+      </c>
+      <c r="T8" t="n">
+        <v>73.6760369898301</v>
+      </c>
+      <c r="U8" t="n">
+        <v>24.66723538776494</v>
+      </c>
+      <c r="V8" t="n">
+        <v>182.6630879663576</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.829801842929922</v>
+      </c>
+      <c r="X8" t="n">
+        <v>73.96264226400311</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>12600829.46476758</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>79.87049116387172</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>27.09090909090909</v>
+      </c>
+      <c r="D9" t="n">
+        <v>182.7935483870968</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.818181818181818</v>
+      </c>
+      <c r="F9" t="n">
+        <v>78.18621700879764</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19782258.06451613</v>
+      </c>
+      <c r="H9" t="n">
+        <v>80.18123167155426</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>25.74133067727037</v>
+      </c>
+      <c r="P9" t="n">
+        <v>181.9924635166921</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.617844715670803</v>
+      </c>
+      <c r="R9" t="n">
+        <v>74.07500344442842</v>
+      </c>
+      <c r="S9" t="n">
+        <v>12741256.89486997</v>
+      </c>
+      <c r="T9" t="n">
+        <v>78.05199891662024</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>25.65993265993266</v>
+      </c>
+      <c r="D14" t="n">
+        <v>185.4680134680135</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.198653198653199</v>
+      </c>
+      <c r="F14" t="n">
+        <v>74.05723905723906</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7525589.225589227</v>
+      </c>
+      <c r="H14" t="n">
+        <v>77.7946127946128</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>24.99453325516544</v>
+      </c>
+      <c r="P14" t="n">
+        <v>184.0568894777707</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.130906416794029</v>
+      </c>
+      <c r="R14" t="n">
+        <v>70.4265359185538</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3774000.20312217</v>
+      </c>
+      <c r="T14" t="n">
+        <v>76.87359558633506</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>26.5939393939394</v>
+      </c>
+      <c r="D15" t="n">
+        <v>183.9142191142191</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.248873348873349</v>
+      </c>
+      <c r="F15" t="n">
+        <v>73.07696192696193</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6264459.013209013</v>
+      </c>
+      <c r="H15" t="n">
+        <v>77.26794871794871</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>25.92492156034011</v>
+      </c>
+      <c r="P15" t="n">
+        <v>184.0404016885578</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.275653228119292</v>
+      </c>
+      <c r="R15" t="n">
+        <v>69.30452076329905</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3189649.25694592</v>
+      </c>
+      <c r="T15" t="n">
+        <v>73.8567595539202</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25.5525641025641</v>
+      </c>
+      <c r="D16" t="n">
+        <v>183.2024087024087</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.314180264180264</v>
+      </c>
+      <c r="F16" t="n">
+        <v>73.88158508158507</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9056600.62160062</v>
+      </c>
+      <c r="H16" t="n">
+        <v>78.63418803418803</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>25.32603438491399</v>
+      </c>
+      <c r="P16" t="n">
+        <v>182.6861701317387</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.197505084411439</v>
+      </c>
+      <c r="R16" t="n">
+        <v>69.9860697351082</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3316996.139629292</v>
+      </c>
+      <c r="T16" t="n">
+        <v>75.71339711756099</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>25.24825174825175</v>
+      </c>
+      <c r="D18" t="n">
+        <v>183.6853146853147</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.038461538461539</v>
+      </c>
+      <c r="F18" t="n">
+        <v>72.25174825174825</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4444405.594405595</v>
+      </c>
+      <c r="H18" t="n">
+        <v>76.72027972027971</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>24.97644022644022</v>
+      </c>
+      <c r="P18" t="n">
+        <v>183.497594179325</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.147562088908243</v>
+      </c>
+      <c r="R18" t="n">
+        <v>69.30581718850951</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3139694.715540869</v>
+      </c>
+      <c r="T18" t="n">
+        <v>74.44231850770312</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>26.87774294670847</v>
+      </c>
+      <c r="D19" t="n">
+        <v>181.9341692789969</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.755485893416928</v>
+      </c>
+      <c r="F19" t="n">
+        <v>80.00940438871473</v>
+      </c>
+      <c r="G19" t="n">
+        <v>32149529.78056427</v>
+      </c>
+      <c r="H19" t="n">
+        <v>82.11285266457681</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>25.16416795042023</v>
+      </c>
+      <c r="P19" t="n">
+        <v>182.1068209937539</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.521203584679083</v>
+      </c>
+      <c r="R19" t="n">
+        <v>74.39943178082925</v>
+      </c>
+      <c r="S19" t="n">
+        <v>13114869.07992693</v>
+      </c>
+      <c r="T19" t="n">
+        <v>78.62138703536162</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>26.1506993006993</v>
+      </c>
+      <c r="D23" t="n">
+        <v>186.0377622377623</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.365734265734266</v>
+      </c>
+      <c r="F23" t="n">
+        <v>75.84545454545454</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12132167.83216783</v>
+      </c>
+      <c r="H23" t="n">
+        <v>79.19405594405595</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>23.80062300695785</v>
+      </c>
+      <c r="P23" t="n">
+        <v>186.7136566048331</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.135395750554122</v>
+      </c>
+      <c r="R23" t="n">
+        <v>70.3368254231942</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4364854.247060129</v>
+      </c>
+      <c r="T23" t="n">
+        <v>76.48432854852538</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>23.58701298701299</v>
+      </c>
+      <c r="D24" t="n">
+        <v>184.5512987012987</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>69.96558441558442</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3335267.857142857</v>
+      </c>
+      <c r="H24" t="n">
+        <v>76.45876623376624</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>24.21326254752363</v>
+      </c>
+      <c r="P24" t="n">
+        <v>183.4007533927485</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>67.26761886353019</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1978090.390498026</v>
+      </c>
+      <c r="T24" t="n">
+        <v>73.49130048386205</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>25.76100823045267</v>
+      </c>
+      <c r="D25" t="n">
+        <v>185.0395061728395</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.18179012345679</v>
+      </c>
+      <c r="F25" t="n">
+        <v>71.74732510288065</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3852420.267489712</v>
+      </c>
+      <c r="H25" t="n">
+        <v>76.50864197530863</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>25.06573132685964</v>
+      </c>
+      <c r="P25" t="n">
+        <v>185.7142757807877</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.138397460748682</v>
+      </c>
+      <c r="R25" t="n">
+        <v>69.55509996921245</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3240982.071692211</v>
+      </c>
+      <c r="T25" t="n">
+        <v>75.45655695640215</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,76 +565,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.5939393939394</v>
+        <v>26.2555023923445</v>
       </c>
       <c r="D2" t="n">
-        <v>183.9142191142191</v>
+        <v>184.1397129186603</v>
       </c>
       <c r="E2" t="n">
-        <v>1.248873348873349</v>
+        <v>1.195215311004785</v>
       </c>
       <c r="F2" t="n">
-        <v>73.07696192696193</v>
+        <v>73.31961722488037</v>
       </c>
       <c r="G2" t="n">
-        <v>6264459.013209013</v>
+        <v>6612428.229665072</v>
       </c>
       <c r="H2" t="n">
-        <v>77.26794871794871</v>
+        <v>77.64114832535886</v>
       </c>
       <c r="I2" t="n">
-        <v>28.34482758620689</v>
+        <v>28.15909090909091</v>
       </c>
       <c r="J2" t="n">
-        <v>182.6677115987461</v>
+        <v>182.3818181818182</v>
       </c>
       <c r="K2" t="n">
-        <v>2.476489028213166</v>
+        <v>2.468181818181818</v>
       </c>
       <c r="L2" t="n">
-        <v>82.77742946708466</v>
+        <v>82.8090909090909</v>
       </c>
       <c r="M2" t="n">
-        <v>39025078.36990596</v>
+        <v>39640909.09090909</v>
       </c>
       <c r="N2" t="n">
-        <v>84.54858934169279</v>
+        <v>84.59090909090909</v>
       </c>
       <c r="O2" t="n">
-        <v>25.92492156034011</v>
+        <v>26.10906278963554</v>
       </c>
       <c r="P2" t="n">
-        <v>184.0404016885578</v>
+        <v>184.8216194331984</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.275653228119292</v>
+        <v>1.359484803122574</v>
       </c>
       <c r="R2" t="n">
-        <v>69.30452076329905</v>
+        <v>69.48319841149564</v>
       </c>
       <c r="S2" t="n">
-        <v>3189649.25694592</v>
+        <v>3263790.357217602</v>
       </c>
       <c r="T2" t="n">
-        <v>73.8567595539202</v>
+        <v>73.75155994160639</v>
       </c>
       <c r="U2" t="n">
-        <v>27.23916141769887</v>
+        <v>27.29508592046523</v>
       </c>
       <c r="V2" t="n">
-        <v>182.7759192232438</v>
+        <v>182.6955991907199</v>
       </c>
       <c r="W2" t="n">
-        <v>1.85578975567085</v>
+        <v>1.932265775093362</v>
       </c>
       <c r="X2" t="n">
-        <v>77.71067894979905</v>
+        <v>78.01517679893541</v>
       </c>
       <c r="Y2" t="n">
-        <v>18106455.36356892</v>
+        <v>19852090.22187902</v>
       </c>
       <c r="Z2" t="n">
-        <v>80.43294715809579</v>
+        <v>80.65667195830989</v>
       </c>
     </row>
     <row r="3">
@@ -653,22 +653,22 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>26.42551319648094</v>
+        <v>26.49717171717172</v>
       </c>
       <c r="J3" t="n">
-        <v>183.1233952427501</v>
+        <v>183.1070707070707</v>
       </c>
       <c r="K3" t="n">
-        <v>1.638937764744216</v>
+        <v>1.654545454545455</v>
       </c>
       <c r="L3" t="n">
-        <v>76.30768980123818</v>
+        <v>76.46898989898989</v>
       </c>
       <c r="M3" t="n">
-        <v>12049116.97621375</v>
+        <v>12393257.57575757</v>
       </c>
       <c r="N3" t="n">
-        <v>79.73929618768327</v>
+        <v>79.63833333333332</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -677,22 +677,22 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>24.42543017472892</v>
+        <v>24.5163890578021</v>
       </c>
       <c r="V3" t="n">
-        <v>183.2220355150019</v>
+        <v>182.5651463717442</v>
       </c>
       <c r="W3" t="n">
-        <v>1.405190466901547</v>
+        <v>1.425837893990068</v>
       </c>
       <c r="X3" t="n">
-        <v>73.10272227798175</v>
+        <v>73.28499329414547</v>
       </c>
       <c r="Y3" t="n">
-        <v>9912293.144884309</v>
+        <v>10517626.13171852</v>
       </c>
       <c r="Z3" t="n">
-        <v>79.10878374495485</v>
+        <v>79.13894511165162</v>
       </c>
     </row>
     <row r="4">
@@ -705,76 +705,76 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.88896103896104</v>
+        <v>25.83636363636364</v>
       </c>
       <c r="D4" t="n">
-        <v>183.9542207792208</v>
+        <v>184.1641148325359</v>
       </c>
       <c r="E4" t="n">
-        <v>1.968506493506494</v>
+        <v>1.939234449760765</v>
       </c>
       <c r="F4" t="n">
-        <v>80.60324675324675</v>
+        <v>80.78612440191388</v>
       </c>
       <c r="G4" t="n">
-        <v>35643766.23376624</v>
+        <v>35939234.44976076</v>
       </c>
       <c r="H4" t="n">
-        <v>84.14350649350649</v>
+        <v>84.11339712918662</v>
       </c>
       <c r="I4" t="n">
-        <v>26.1506993006993</v>
+        <v>26.13540669856459</v>
       </c>
       <c r="J4" t="n">
-        <v>186.0377622377623</v>
+        <v>186.2177033492823</v>
       </c>
       <c r="K4" t="n">
-        <v>1.365734265734266</v>
+        <v>1.345933014354067</v>
       </c>
       <c r="L4" t="n">
-        <v>75.84545454545454</v>
+        <v>75.70526315789475</v>
       </c>
       <c r="M4" t="n">
-        <v>12132167.83216783</v>
+        <v>11967655.50239235</v>
       </c>
       <c r="N4" t="n">
-        <v>79.19405594405595</v>
+        <v>78.98373205741628</v>
       </c>
       <c r="O4" t="n">
-        <v>23.97172401799404</v>
+        <v>24.61388432417699</v>
       </c>
       <c r="P4" t="n">
-        <v>183.0353403019135</v>
+        <v>183.8259792950146</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.434322284207868</v>
+        <v>1.526207602354778</v>
       </c>
       <c r="R4" t="n">
-        <v>72.81321493575498</v>
+        <v>74.96575635390522</v>
       </c>
       <c r="S4" t="n">
-        <v>13622612.46019427</v>
+        <v>16451315.87987267</v>
       </c>
       <c r="T4" t="n">
-        <v>80.96641507255352</v>
+        <v>81.46254639865023</v>
       </c>
       <c r="U4" t="n">
-        <v>23.80062300695785</v>
+        <v>24.07371712892326</v>
       </c>
       <c r="V4" t="n">
-        <v>186.7136566048331</v>
+        <v>186.2325411991373</v>
       </c>
       <c r="W4" t="n">
-        <v>1.135395750554122</v>
+        <v>1.176680160858098</v>
       </c>
       <c r="X4" t="n">
-        <v>70.3368254231942</v>
+        <v>70.70015071335341</v>
       </c>
       <c r="Y4" t="n">
-        <v>4364854.247060129</v>
+        <v>4672714.393404471</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.48432854852538</v>
+        <v>76.29963134334571</v>
       </c>
     </row>
     <row r="5">
@@ -787,76 +787,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.24825174825175</v>
+        <v>25.2979797979798</v>
       </c>
       <c r="D5" t="n">
-        <v>183.6853146853147</v>
+        <v>183.8989898989899</v>
       </c>
       <c r="E5" t="n">
-        <v>1.038461538461539</v>
+        <v>1.045454545454546</v>
       </c>
       <c r="F5" t="n">
-        <v>72.25174825174825</v>
+        <v>72.43434343434343</v>
       </c>
       <c r="G5" t="n">
-        <v>4444405.594405595</v>
+        <v>4593939.393939395</v>
       </c>
       <c r="H5" t="n">
-        <v>76.72027972027971</v>
+        <v>76.40909090909092</v>
       </c>
       <c r="I5" t="n">
-        <v>25.5525641025641</v>
+        <v>25.09649122807018</v>
       </c>
       <c r="J5" t="n">
-        <v>183.2024087024087</v>
+        <v>182.9666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>1.314180264180264</v>
+        <v>1.285964912280702</v>
       </c>
       <c r="L5" t="n">
-        <v>73.88158508158507</v>
+        <v>73.67660818713449</v>
       </c>
       <c r="M5" t="n">
-        <v>9056600.62160062</v>
+        <v>8849298.245614035</v>
       </c>
       <c r="N5" t="n">
-        <v>78.63418803418803</v>
+        <v>78.68654970760232</v>
       </c>
       <c r="O5" t="n">
-        <v>24.97644022644022</v>
+        <v>25.40753875753876</v>
       </c>
       <c r="P5" t="n">
-        <v>183.497594179325</v>
+        <v>183.3722598389265</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.147562088908243</v>
+        <v>1.168166607055496</v>
       </c>
       <c r="R5" t="n">
-        <v>69.30581718850951</v>
+        <v>69.21181534514868</v>
       </c>
       <c r="S5" t="n">
-        <v>3139694.715540869</v>
+        <v>2532675.91307869</v>
       </c>
       <c r="T5" t="n">
-        <v>74.44231850770312</v>
+        <v>73.73546504935393</v>
       </c>
       <c r="U5" t="n">
-        <v>25.32603438491399</v>
+        <v>25.43478395746131</v>
       </c>
       <c r="V5" t="n">
-        <v>182.6861701317387</v>
+        <v>182.9528915994591</v>
       </c>
       <c r="W5" t="n">
-        <v>1.197505084411439</v>
+        <v>1.232163582667015</v>
       </c>
       <c r="X5" t="n">
-        <v>69.9860697351082</v>
+        <v>70.7764393598604</v>
       </c>
       <c r="Y5" t="n">
-        <v>3316996.139629292</v>
+        <v>3598983.947074622</v>
       </c>
       <c r="Z5" t="n">
-        <v>75.71339711756099</v>
+        <v>76.08541191243708</v>
       </c>
     </row>
     <row r="6">
@@ -869,76 +869,76 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.41558441558442</v>
+        <v>24.52727272727272</v>
       </c>
       <c r="D6" t="n">
-        <v>185.2467532467533</v>
+        <v>185.2590909090909</v>
       </c>
       <c r="E6" t="n">
-        <v>1.266233766233767</v>
+        <v>1.277272727272728</v>
       </c>
       <c r="F6" t="n">
-        <v>75.07792207792207</v>
+        <v>75.24090909090908</v>
       </c>
       <c r="G6" t="n">
-        <v>11093181.81818182</v>
+        <v>11404204.54545455</v>
       </c>
       <c r="H6" t="n">
-        <v>80.07467532467533</v>
+        <v>79.9409090909091</v>
       </c>
       <c r="I6" t="n">
-        <v>24.82867132867133</v>
+        <v>25.1010101010101</v>
       </c>
       <c r="J6" t="n">
-        <v>186.0636363636363</v>
+        <v>186.4393939393939</v>
       </c>
       <c r="K6" t="n">
-        <v>1.057342657342657</v>
+        <v>1.050505050505051</v>
       </c>
       <c r="L6" t="n">
-        <v>73.10314685314685</v>
+        <v>73.2929292929293</v>
       </c>
       <c r="M6" t="n">
-        <v>5359720.279720278</v>
+        <v>5193434.343434344</v>
       </c>
       <c r="N6" t="n">
-        <v>77.61748251748251</v>
+        <v>77.22222222222223</v>
       </c>
       <c r="O6" t="n">
-        <v>23.57238459816046</v>
+        <v>23.17949529844357</v>
       </c>
       <c r="P6" t="n">
-        <v>185.6021287661436</v>
+        <v>185.153879513845</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.179637896312773</v>
+        <v>1.189672975172975</v>
       </c>
       <c r="R6" t="n">
-        <v>70.17567077080008</v>
+        <v>70.3836387029318</v>
       </c>
       <c r="S6" t="n">
-        <v>5404430.919808844</v>
+        <v>5934669.931441483</v>
       </c>
       <c r="T6" t="n">
-        <v>77.19984893048932</v>
+        <v>77.4097358777876</v>
       </c>
       <c r="U6" t="n">
-        <v>25.46507138872524</v>
+        <v>25.3698263567708</v>
       </c>
       <c r="V6" t="n">
-        <v>184.0301636042021</v>
+        <v>183.5453445114556</v>
       </c>
       <c r="W6" t="n">
-        <v>1.089346945789254</v>
+        <v>1.088193858610525</v>
       </c>
       <c r="X6" t="n">
-        <v>70.11500447913909</v>
+        <v>70.46529340515451</v>
       </c>
       <c r="Y6" t="n">
-        <v>2964692.404817405</v>
+        <v>3050955.941178164</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.96886243386244</v>
+        <v>74.75181527834305</v>
       </c>
     </row>
     <row r="7">
@@ -951,76 +951,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>24.8034965034965</v>
+        <v>25.11004784688996</v>
       </c>
       <c r="D7" t="n">
-        <v>184.1674825174825</v>
+        <v>184.1387559808612</v>
       </c>
       <c r="E7" t="n">
-        <v>1.139510489510489</v>
+        <v>1.15311004784689</v>
       </c>
       <c r="F7" t="n">
-        <v>73.02692307692308</v>
+        <v>73.01435406698565</v>
       </c>
       <c r="G7" t="n">
-        <v>5162534.965034964</v>
+        <v>4804665.071770336</v>
       </c>
       <c r="H7" t="n">
-        <v>77.31083916083915</v>
+        <v>76.62200956937799</v>
       </c>
       <c r="I7" t="n">
-        <v>26.87774294670847</v>
+        <v>26.87727272727273</v>
       </c>
       <c r="J7" t="n">
-        <v>181.9341692789969</v>
+        <v>181.7954545454546</v>
       </c>
       <c r="K7" t="n">
-        <v>1.755485893416928</v>
+        <v>1.745454545454545</v>
       </c>
       <c r="L7" t="n">
-        <v>80.00940438871473</v>
+        <v>80.25</v>
       </c>
       <c r="M7" t="n">
-        <v>32149529.78056427</v>
+        <v>32505909.09090909</v>
       </c>
       <c r="N7" t="n">
-        <v>82.11285266457681</v>
+        <v>82</v>
       </c>
       <c r="O7" t="n">
-        <v>24.25122708488093</v>
+        <v>23.88974665685192</v>
       </c>
       <c r="P7" t="n">
-        <v>184.3228549228549</v>
+        <v>183.3524330445383</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.042764998534229</v>
+        <v>1.024993038150933</v>
       </c>
       <c r="R7" t="n">
-        <v>69.48662100008254</v>
+        <v>69.73448091869145</v>
       </c>
       <c r="S7" t="n">
-        <v>2802540.783646553</v>
+        <v>2936683.328854382</v>
       </c>
       <c r="T7" t="n">
-        <v>74.6287192864116</v>
+        <v>74.98771408902988</v>
       </c>
       <c r="U7" t="n">
-        <v>25.16416795042023</v>
+        <v>25.26171777053356</v>
       </c>
       <c r="V7" t="n">
-        <v>182.1068209937539</v>
+        <v>182.1137667035694</v>
       </c>
       <c r="W7" t="n">
-        <v>1.521203584679083</v>
+        <v>1.542319873109347</v>
       </c>
       <c r="X7" t="n">
-        <v>74.39943178082925</v>
+        <v>75.27106461034093</v>
       </c>
       <c r="Y7" t="n">
-        <v>13114869.07992693</v>
+        <v>13390042.93531761</v>
       </c>
       <c r="Z7" t="n">
-        <v>78.62138703536162</v>
+        <v>78.81953215644005</v>
       </c>
     </row>
     <row r="8">
@@ -1033,76 +1033,76 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.8013468013468</v>
+        <v>25.80808080808081</v>
       </c>
       <c r="D8" t="n">
-        <v>184.6498316498316</v>
+        <v>184.4949494949495</v>
       </c>
       <c r="E8" t="n">
-        <v>1.232323232323233</v>
+        <v>1.257575757575758</v>
       </c>
       <c r="F8" t="n">
-        <v>72.12794612794613</v>
+        <v>72.24747474747475</v>
       </c>
       <c r="G8" t="n">
-        <v>3405134.680134681</v>
+        <v>3544949.494949495</v>
       </c>
       <c r="H8" t="n">
-        <v>75.64309764309765</v>
+        <v>75.46969696969697</v>
       </c>
       <c r="I8" t="n">
-        <v>27.26118326118326</v>
+        <v>26.84736842105263</v>
       </c>
       <c r="J8" t="n">
-        <v>183.0731240981241</v>
+        <v>182.474269005848</v>
       </c>
       <c r="K8" t="n">
-        <v>2.28946608946609</v>
+        <v>2.259649122807018</v>
       </c>
       <c r="L8" t="n">
-        <v>78.86031746031745</v>
+        <v>78.67368421052633</v>
       </c>
       <c r="M8" t="n">
-        <v>21180660.17316017</v>
+        <v>21076081.87134503</v>
       </c>
       <c r="N8" t="n">
-        <v>80.80743145743146</v>
+        <v>80.54210526315791</v>
       </c>
       <c r="O8" t="n">
-        <v>26.37323376921078</v>
+        <v>25.81022706539948</v>
       </c>
       <c r="P8" t="n">
-        <v>184.1473743582939</v>
+        <v>183.757651575755</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.169356229126344</v>
+        <v>1.128747657195933</v>
       </c>
       <c r="R8" t="n">
-        <v>69.79790777549398</v>
+        <v>69.98425444287513</v>
       </c>
       <c r="S8" t="n">
-        <v>2347848.359601233</v>
+        <v>2639623.334519886</v>
       </c>
       <c r="T8" t="n">
-        <v>73.6760369898301</v>
+        <v>74.31963154980397</v>
       </c>
       <c r="U8" t="n">
-        <v>24.66723538776494</v>
+        <v>24.81503405581445</v>
       </c>
       <c r="V8" t="n">
-        <v>182.6630879663576</v>
+        <v>182.5881161666189</v>
       </c>
       <c r="W8" t="n">
-        <v>1.829801842929922</v>
+        <v>1.87133231962633</v>
       </c>
       <c r="X8" t="n">
-        <v>73.96264226400311</v>
+        <v>74.82057456994843</v>
       </c>
       <c r="Y8" t="n">
-        <v>12600829.46476758</v>
+        <v>13803595.86864033</v>
       </c>
       <c r="Z8" t="n">
-        <v>79.87049116387172</v>
+        <v>80.25960823373708</v>
       </c>
     </row>
     <row r="9">
@@ -1115,22 +1115,22 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>27.09090909090909</v>
+        <v>27.22683982683983</v>
       </c>
       <c r="D9" t="n">
-        <v>182.7935483870968</v>
+        <v>182.9428571428572</v>
       </c>
       <c r="E9" t="n">
-        <v>1.818181818181818</v>
+        <v>1.868398268398268</v>
       </c>
       <c r="F9" t="n">
-        <v>78.18621700879764</v>
+        <v>78.24761904761904</v>
       </c>
       <c r="G9" t="n">
-        <v>19782258.06451613</v>
+        <v>19695584.41558442</v>
       </c>
       <c r="H9" t="n">
-        <v>80.18123167155426</v>
+        <v>80.15454545454547</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1139,22 +1139,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>25.74133067727037</v>
+        <v>25.80220522173938</v>
       </c>
       <c r="P9" t="n">
-        <v>181.9924635166921</v>
+        <v>181.8394692735376</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.617844715670803</v>
+        <v>1.680378480502704</v>
       </c>
       <c r="R9" t="n">
-        <v>74.07500344442842</v>
+        <v>74.5140993857764</v>
       </c>
       <c r="S9" t="n">
-        <v>12741256.89486997</v>
+        <v>13875644.45823902</v>
       </c>
       <c r="T9" t="n">
-        <v>78.05199891662024</v>
+        <v>78.35601894424876</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
@@ -1166,60 +1166,136 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>24.2822966507177</v>
+      </c>
+      <c r="D10" t="n">
+        <v>184.2344497607655</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.00956937799043</v>
+      </c>
+      <c r="F10" t="n">
+        <v>72.19617224880383</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5071531.100478468</v>
+      </c>
+      <c r="H10" t="n">
+        <v>77.51674641148327</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25.56459330143541</v>
+      </c>
+      <c r="J10" t="n">
+        <v>187.1961722488038</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.492822966507177</v>
+      </c>
+      <c r="L10" t="n">
+        <v>78.26315789473684</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19310287.08133971</v>
+      </c>
+      <c r="N10" t="n">
+        <v>81.83253588516747</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23.0853502104303</v>
+      </c>
+      <c r="P10" t="n">
+        <v>182.9018937126946</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.077260405498392</v>
+      </c>
+      <c r="R10" t="n">
+        <v>67.42196572306412</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2433707.509881423</v>
+      </c>
+      <c r="T10" t="n">
+        <v>74.63821286265221</v>
+      </c>
+      <c r="U10" t="n">
+        <v>25.89604615657247</v>
+      </c>
+      <c r="V10" t="n">
+        <v>186.6926368271105</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.406213484371379</v>
+      </c>
+      <c r="X10" t="n">
+        <v>74.59795887348518</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>12306264.27738928</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>78.42471789419157</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25.64508240297714</v>
+      </c>
+      <c r="D11" t="n">
+        <v>185.8693248272195</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.892729930887825</v>
+      </c>
+      <c r="F11" t="n">
+        <v>80.73540669856459</v>
+      </c>
+      <c r="G11" t="n">
+        <v>31045049.17597023</v>
+      </c>
+      <c r="H11" t="n">
+        <v>84.19424508240297</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>24.42791990985716</v>
+      </c>
+      <c r="P11" t="n">
+        <v>184.2685344133164</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.639830028924332</v>
+      </c>
+      <c r="R11" t="n">
+        <v>74.91975179262906</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14242823.83156073</v>
+      </c>
+      <c r="T11" t="n">
+        <v>80.92671915382383</v>
+      </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -1230,7 +1306,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>f9bfyqFM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1262,7 +1338,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>bHLf4sq9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1294,54 +1370,28 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>25.65993265993266</v>
-      </c>
-      <c r="D14" t="n">
-        <v>185.4680134680135</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.198653198653199</v>
-      </c>
-      <c r="F14" t="n">
-        <v>74.05723905723906</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7525589.225589227</v>
-      </c>
-      <c r="H14" t="n">
-        <v>77.7946127946128</v>
-      </c>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>24.99453325516544</v>
-      </c>
-      <c r="P14" t="n">
-        <v>184.0568894777707</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.130906416794029</v>
-      </c>
-      <c r="R14" t="n">
-        <v>70.4265359185538</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3774000.20312217</v>
-      </c>
-      <c r="T14" t="n">
-        <v>76.87359558633506</v>
-      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -1352,54 +1402,28 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>26.5939393939394</v>
-      </c>
-      <c r="D15" t="n">
-        <v>183.9142191142191</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.248873348873349</v>
-      </c>
-      <c r="F15" t="n">
-        <v>73.07696192696193</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6264459.013209013</v>
-      </c>
-      <c r="H15" t="n">
-        <v>77.26794871794871</v>
-      </c>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>25.92492156034011</v>
-      </c>
-      <c r="P15" t="n">
-        <v>184.0404016885578</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.275653228119292</v>
-      </c>
-      <c r="R15" t="n">
-        <v>69.30452076329905</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3189649.25694592</v>
-      </c>
-      <c r="T15" t="n">
-        <v>73.8567595539202</v>
-      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -1410,29 +1434,29 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>25.5525641025641</v>
+        <v>25.65909090909091</v>
       </c>
       <c r="D16" t="n">
-        <v>183.2024087024087</v>
+        <v>185.7545454545455</v>
       </c>
       <c r="E16" t="n">
-        <v>1.314180264180264</v>
+        <v>1.186363636363637</v>
       </c>
       <c r="F16" t="n">
-        <v>73.88158508158507</v>
+        <v>73.7409090909091</v>
       </c>
       <c r="G16" t="n">
-        <v>9056600.62160062</v>
+        <v>6301590.909090909</v>
       </c>
       <c r="H16" t="n">
-        <v>78.63418803418803</v>
+        <v>77.56363636363636</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1441,22 +1465,22 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>25.32603438491399</v>
+        <v>24.85683886994232</v>
       </c>
       <c r="P16" t="n">
-        <v>182.6861701317387</v>
+        <v>184.4361339793667</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.197505084411439</v>
+        <v>1.138439585637862</v>
       </c>
       <c r="R16" t="n">
-        <v>69.9860697351082</v>
+        <v>70.6468399735641</v>
       </c>
       <c r="S16" t="n">
-        <v>3316996.139629292</v>
+        <v>3809298.473238128</v>
       </c>
       <c r="T16" t="n">
-        <v>75.71339711756099</v>
+        <v>76.88788009882838</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1468,28 +1492,54 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26.2555023923445</v>
+      </c>
+      <c r="D17" t="n">
+        <v>184.1397129186603</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.195215311004785</v>
+      </c>
+      <c r="F17" t="n">
+        <v>73.31961722488037</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6612428.229665072</v>
+      </c>
+      <c r="H17" t="n">
+        <v>77.64114832535886</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>26.10906278963554</v>
+      </c>
+      <c r="P17" t="n">
+        <v>184.8216194331984</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.359484803122574</v>
+      </c>
+      <c r="R17" t="n">
+        <v>69.48319841149564</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3263790.357217602</v>
+      </c>
+      <c r="T17" t="n">
+        <v>73.75155994160639</v>
+      </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
@@ -1500,29 +1550,29 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25.24825174825175</v>
+        <v>25.09649122807018</v>
       </c>
       <c r="D18" t="n">
-        <v>183.6853146853147</v>
+        <v>182.9666666666666</v>
       </c>
       <c r="E18" t="n">
-        <v>1.038461538461539</v>
+        <v>1.285964912280702</v>
       </c>
       <c r="F18" t="n">
-        <v>72.25174825174825</v>
+        <v>73.67660818713449</v>
       </c>
       <c r="G18" t="n">
-        <v>4444405.594405595</v>
+        <v>8849298.245614035</v>
       </c>
       <c r="H18" t="n">
-        <v>76.72027972027971</v>
+        <v>78.68654970760232</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1531,22 +1581,22 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>24.97644022644022</v>
+        <v>25.43478395746131</v>
       </c>
       <c r="P18" t="n">
-        <v>183.497594179325</v>
+        <v>182.9528915994591</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.147562088908243</v>
+        <v>1.232163582667015</v>
       </c>
       <c r="R18" t="n">
-        <v>69.30581718850951</v>
+        <v>70.7764393598604</v>
       </c>
       <c r="S18" t="n">
-        <v>3139694.715540869</v>
+        <v>3598983.947074622</v>
       </c>
       <c r="T18" t="n">
-        <v>74.44231850770312</v>
+        <v>76.08541191243708</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -1558,54 +1608,28 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>26.87774294670847</v>
-      </c>
-      <c r="D19" t="n">
-        <v>181.9341692789969</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.755485893416928</v>
-      </c>
-      <c r="F19" t="n">
-        <v>80.00940438871473</v>
-      </c>
-      <c r="G19" t="n">
-        <v>32149529.78056427</v>
-      </c>
-      <c r="H19" t="n">
-        <v>82.11285266457681</v>
-      </c>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>25.16416795042023</v>
-      </c>
-      <c r="P19" t="n">
-        <v>182.1068209937539</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.521203584679083</v>
-      </c>
-      <c r="R19" t="n">
-        <v>74.39943178082925</v>
-      </c>
-      <c r="S19" t="n">
-        <v>13114869.07992693</v>
-      </c>
-      <c r="T19" t="n">
-        <v>78.62138703536162</v>
-      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
@@ -1616,28 +1640,54 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>25.2979797979798</v>
+      </c>
+      <c r="D20" t="n">
+        <v>183.8989898989899</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.045454545454546</v>
+      </c>
+      <c r="F20" t="n">
+        <v>72.43434343434343</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4593939.393939395</v>
+      </c>
+      <c r="H20" t="n">
+        <v>76.40909090909092</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>25.40753875753876</v>
+      </c>
+      <c r="P20" t="n">
+        <v>183.3722598389265</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.168166607055496</v>
+      </c>
+      <c r="R20" t="n">
+        <v>69.21181534514868</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2532675.91307869</v>
+      </c>
+      <c r="T20" t="n">
+        <v>73.73546504935393</v>
+      </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
@@ -1648,28 +1698,54 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>26.87727272727273</v>
+      </c>
+      <c r="D21" t="n">
+        <v>181.7954545454546</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.745454545454545</v>
+      </c>
+      <c r="F21" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="G21" t="n">
+        <v>32505909.09090909</v>
+      </c>
+      <c r="H21" t="n">
+        <v>82</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>25.26171777053356</v>
+      </c>
+      <c r="P21" t="n">
+        <v>182.1137667035694</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.542319873109347</v>
+      </c>
+      <c r="R21" t="n">
+        <v>75.27106461034093</v>
+      </c>
+      <c r="S21" t="n">
+        <v>13390042.93531761</v>
+      </c>
+      <c r="T21" t="n">
+        <v>78.81953215644005</v>
+      </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
@@ -1680,7 +1756,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1712,54 +1788,28 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>26.1506993006993</v>
-      </c>
-      <c r="D23" t="n">
-        <v>186.0377622377623</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.365734265734266</v>
-      </c>
-      <c r="F23" t="n">
-        <v>75.84545454545454</v>
-      </c>
-      <c r="G23" t="n">
-        <v>12132167.83216783</v>
-      </c>
-      <c r="H23" t="n">
-        <v>79.19405594405595</v>
-      </c>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>23.80062300695785</v>
-      </c>
-      <c r="P23" t="n">
-        <v>186.7136566048331</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.135395750554122</v>
-      </c>
-      <c r="R23" t="n">
-        <v>70.3368254231942</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4364854.247060129</v>
-      </c>
-      <c r="T23" t="n">
-        <v>76.48432854852538</v>
-      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
@@ -1770,54 +1820,28 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="n">
-        <v>23.58701298701299</v>
-      </c>
-      <c r="D24" t="n">
-        <v>184.5512987012987</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>69.96558441558442</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3335267.857142857</v>
-      </c>
-      <c r="H24" t="n">
-        <v>76.45876623376624</v>
-      </c>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>24.21326254752363</v>
-      </c>
-      <c r="P24" t="n">
-        <v>183.4007533927485</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>67.26761886353019</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1978090.390498026</v>
-      </c>
-      <c r="T24" t="n">
-        <v>73.49130048386205</v>
-      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
@@ -1828,29 +1852,29 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>25.76100823045267</v>
+        <v>26.13540669856459</v>
       </c>
       <c r="D25" t="n">
-        <v>185.0395061728395</v>
+        <v>186.2177033492823</v>
       </c>
       <c r="E25" t="n">
-        <v>1.18179012345679</v>
+        <v>1.345933014354067</v>
       </c>
       <c r="F25" t="n">
-        <v>71.74732510288065</v>
+        <v>75.70526315789475</v>
       </c>
       <c r="G25" t="n">
-        <v>3852420.267489712</v>
+        <v>11967655.50239235</v>
       </c>
       <c r="H25" t="n">
-        <v>76.50864197530863</v>
+        <v>78.98373205741628</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -1859,22 +1883,22 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>25.06573132685964</v>
+        <v>24.07371712892326</v>
       </c>
       <c r="P25" t="n">
-        <v>185.7142757807877</v>
+        <v>186.2325411991373</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.138397460748682</v>
+        <v>1.176680160858098</v>
       </c>
       <c r="R25" t="n">
-        <v>69.55509996921245</v>
+        <v>70.70015071335341</v>
       </c>
       <c r="S25" t="n">
-        <v>3240982.071692211</v>
+        <v>4672714.393404471</v>
       </c>
       <c r="T25" t="n">
-        <v>75.45655695640215</v>
+        <v>76.29963134334571</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -1883,6 +1907,520 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>23.89665071770335</v>
+      </c>
+      <c r="D26" t="n">
+        <v>184.5736842105263</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>70.6645933014354</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3936411.483253589</v>
+      </c>
+      <c r="H26" t="n">
+        <v>76.43540669856458</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>23.74312561203669</v>
+      </c>
+      <c r="P26" t="n">
+        <v>183.6335690322987</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>67.26407692462139</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2169314.78978439</v>
+      </c>
+      <c r="T26" t="n">
+        <v>73.99388850042207</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>25.48011695906433</v>
+      </c>
+      <c r="D27" t="n">
+        <v>184.7134502923977</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.184795321637427</v>
+      </c>
+      <c r="F27" t="n">
+        <v>71.70877192982455</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3679389.619883041</v>
+      </c>
+      <c r="H27" t="n">
+        <v>76.68830409356725</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>24.6741246188859</v>
+      </c>
+      <c r="P27" t="n">
+        <v>184.6261118048392</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.180213963430519</v>
+      </c>
+      <c r="R27" t="n">
+        <v>69.8347690796159</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3509979.030992454</v>
+      </c>
+      <c r="T27" t="n">
+        <v>75.79803688833753</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>25.48011695906433</v>
+      </c>
+      <c r="D31" t="n">
+        <v>184.7134502923977</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.184795321637427</v>
+      </c>
+      <c r="F31" t="n">
+        <v>71.70877192982455</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3679389.619883041</v>
+      </c>
+      <c r="H31" t="n">
+        <v>76.68830409356725</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>24.6741246188859</v>
+      </c>
+      <c r="P31" t="n">
+        <v>184.6261118048392</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.180213963430519</v>
+      </c>
+      <c r="R31" t="n">
+        <v>69.8347690796159</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3509979.030992454</v>
+      </c>
+      <c r="T31" t="n">
+        <v>75.79803688833753</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>25.65909090909091</v>
+      </c>
+      <c r="J33" t="n">
+        <v>185.7545454545455</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.186363636363637</v>
+      </c>
+      <c r="L33" t="n">
+        <v>73.7409090909091</v>
+      </c>
+      <c r="M33" t="n">
+        <v>6301590.909090909</v>
+      </c>
+      <c r="N33" t="n">
+        <v>77.56363636363636</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>24.85683886994232</v>
+      </c>
+      <c r="V33" t="n">
+        <v>184.4361339793667</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.138439585637862</v>
+      </c>
+      <c r="X33" t="n">
+        <v>70.6468399735641</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>3809298.473238128</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>76.88788009882838</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>23.89665071770335</v>
+      </c>
+      <c r="D36" t="n">
+        <v>184.5736842105263</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>70.6645933014354</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3936411.483253589</v>
+      </c>
+      <c r="H36" t="n">
+        <v>76.43540669856458</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>23.74312561203669</v>
+      </c>
+      <c r="P36" t="n">
+        <v>183.6335690322987</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>67.26407692462139</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2169314.78978439</v>
+      </c>
+      <c r="T36" t="n">
+        <v>73.99388850042207</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -565,76 +565,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.2555023923445</v>
+        <v>26.29772727272727</v>
       </c>
       <c r="D2" t="n">
-        <v>184.1397129186603</v>
+        <v>184.0636363636364</v>
       </c>
       <c r="E2" t="n">
-        <v>1.195215311004785</v>
+        <v>1.192045454545455</v>
       </c>
       <c r="F2" t="n">
-        <v>73.31961722488037</v>
+        <v>73.4465909090909</v>
       </c>
       <c r="G2" t="n">
-        <v>6612428.229665072</v>
+        <v>6644872.159090909</v>
       </c>
       <c r="H2" t="n">
-        <v>77.64114832535886</v>
+        <v>77.7</v>
       </c>
       <c r="I2" t="n">
-        <v>28.15909090909091</v>
+        <v>27.99304812834225</v>
       </c>
       <c r="J2" t="n">
-        <v>182.3818181818182</v>
+        <v>182.7208556149733</v>
       </c>
       <c r="K2" t="n">
-        <v>2.468181818181818</v>
+        <v>2.428877005347593</v>
       </c>
       <c r="L2" t="n">
-        <v>82.8090909090909</v>
+        <v>82.85401069518717</v>
       </c>
       <c r="M2" t="n">
-        <v>39640909.09090909</v>
+        <v>40003743.31550803</v>
       </c>
       <c r="N2" t="n">
-        <v>84.59090909090909</v>
+        <v>84.67272727272727</v>
       </c>
       <c r="O2" t="n">
-        <v>26.10906278963554</v>
+        <v>26.65860588553603</v>
       </c>
       <c r="P2" t="n">
-        <v>184.8216194331984</v>
+        <v>184.5409919883357</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.359484803122574</v>
+        <v>1.39986415715276</v>
       </c>
       <c r="R2" t="n">
-        <v>69.48319841149564</v>
+        <v>70.64037415913336</v>
       </c>
       <c r="S2" t="n">
-        <v>3263790.357217602</v>
+        <v>3742602.524832534</v>
       </c>
       <c r="T2" t="n">
-        <v>73.75155994160639</v>
+        <v>74.10767259429025</v>
       </c>
       <c r="U2" t="n">
-        <v>27.29508592046523</v>
+        <v>27.105357461048</v>
       </c>
       <c r="V2" t="n">
-        <v>182.6955991907199</v>
+        <v>183.2180354186876</v>
       </c>
       <c r="W2" t="n">
-        <v>1.932265775093362</v>
+        <v>1.917764056536435</v>
       </c>
       <c r="X2" t="n">
-        <v>78.01517679893541</v>
+        <v>78.86880391891903</v>
       </c>
       <c r="Y2" t="n">
-        <v>19852090.22187902</v>
+        <v>24021291.4686313</v>
       </c>
       <c r="Z2" t="n">
-        <v>80.65667195830989</v>
+        <v>81.43710115166635</v>
       </c>
     </row>
     <row r="3">
@@ -646,53 +646,77 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>24.83522727272727</v>
+      </c>
+      <c r="D3" t="n">
+        <v>185.2846590909091</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.048295454545455</v>
+      </c>
+      <c r="F3" t="n">
+        <v>70.28352272727273</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3159488.636363637</v>
+      </c>
+      <c r="H3" t="n">
+        <v>75.71704545454546</v>
+      </c>
       <c r="I3" t="n">
-        <v>26.49717171717172</v>
+        <v>26.47272727272727</v>
       </c>
       <c r="J3" t="n">
-        <v>183.1070707070707</v>
+        <v>183.299043062201</v>
       </c>
       <c r="K3" t="n">
-        <v>1.654545454545455</v>
+        <v>1.659808612440191</v>
       </c>
       <c r="L3" t="n">
-        <v>76.46898989898989</v>
+        <v>76.55263157894737</v>
       </c>
       <c r="M3" t="n">
-        <v>12393257.57575757</v>
+        <v>12639234.44976077</v>
       </c>
       <c r="N3" t="n">
-        <v>79.63833333333332</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+        <v>79.59282296650717</v>
+      </c>
+      <c r="O3" t="n">
+        <v>24.6143007556051</v>
+      </c>
+      <c r="P3" t="n">
+        <v>184.460542665366</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.093067748978075</v>
+      </c>
+      <c r="R3" t="n">
+        <v>68.31454288213799</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2369897.367188468</v>
+      </c>
+      <c r="T3" t="n">
+        <v>73.64909265452744</v>
+      </c>
       <c r="U3" t="n">
-        <v>24.5163890578021</v>
+        <v>25.18913312991139</v>
       </c>
       <c r="V3" t="n">
-        <v>182.5651463717442</v>
+        <v>181.7304426151949</v>
       </c>
       <c r="W3" t="n">
-        <v>1.425837893990068</v>
+        <v>1.555732653951453</v>
       </c>
       <c r="X3" t="n">
-        <v>73.28499329414547</v>
+        <v>74.66489422349525</v>
       </c>
       <c r="Y3" t="n">
-        <v>10517626.13171852</v>
+        <v>11666847.64528231</v>
       </c>
       <c r="Z3" t="n">
-        <v>79.13894511165162</v>
+        <v>79.10342347760094</v>
       </c>
     </row>
     <row r="4">
@@ -705,76 +729,76 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.83636363636364</v>
+        <v>25.47935606060606</v>
       </c>
       <c r="D4" t="n">
-        <v>184.1641148325359</v>
+        <v>184.7681186868687</v>
       </c>
       <c r="E4" t="n">
-        <v>1.939234449760765</v>
+        <v>1.867234848484848</v>
       </c>
       <c r="F4" t="n">
-        <v>80.78612440191388</v>
+        <v>80.88080808080809</v>
       </c>
       <c r="G4" t="n">
-        <v>35939234.44976076</v>
+        <v>36151303.66161616</v>
       </c>
       <c r="H4" t="n">
-        <v>84.11339712918662</v>
+        <v>84.36047979797981</v>
       </c>
       <c r="I4" t="n">
-        <v>26.13540669856459</v>
+        <v>25.89946524064171</v>
       </c>
       <c r="J4" t="n">
-        <v>186.2177033492823</v>
+        <v>186.2572192513369</v>
       </c>
       <c r="K4" t="n">
-        <v>1.345933014354067</v>
+        <v>1.275935828877006</v>
       </c>
       <c r="L4" t="n">
-        <v>75.70526315789475</v>
+        <v>75.78983957219252</v>
       </c>
       <c r="M4" t="n">
-        <v>11967655.50239235</v>
+        <v>12650855.61497326</v>
       </c>
       <c r="N4" t="n">
-        <v>78.98373205741628</v>
+        <v>79.04010695187166</v>
       </c>
       <c r="O4" t="n">
-        <v>24.61388432417699</v>
+        <v>24.48059814682097</v>
       </c>
       <c r="P4" t="n">
-        <v>183.8259792950146</v>
+        <v>184.004159411442</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.526207602354778</v>
+        <v>1.532936098724142</v>
       </c>
       <c r="R4" t="n">
-        <v>74.96575635390522</v>
+        <v>76.37470707030489</v>
       </c>
       <c r="S4" t="n">
-        <v>16451315.87987267</v>
+        <v>20609008.02222133</v>
       </c>
       <c r="T4" t="n">
-        <v>81.46254639865023</v>
+        <v>82.22238245651289</v>
       </c>
       <c r="U4" t="n">
-        <v>24.07371712892326</v>
+        <v>24.57152140523933</v>
       </c>
       <c r="V4" t="n">
-        <v>186.2325411991373</v>
+        <v>185.391205899366</v>
       </c>
       <c r="W4" t="n">
-        <v>1.176680160858098</v>
+        <v>1.16637106491948</v>
       </c>
       <c r="X4" t="n">
-        <v>70.70015071335341</v>
+        <v>72.04009418022972</v>
       </c>
       <c r="Y4" t="n">
-        <v>4672714.393404471</v>
+        <v>6506192.078869222</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.29963134334571</v>
+        <v>76.63134153362353</v>
       </c>
     </row>
     <row r="5">
@@ -787,76 +811,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.2979797979798</v>
+        <v>25.26704545454545</v>
       </c>
       <c r="D5" t="n">
-        <v>183.8989898989899</v>
+        <v>183.9318181818182</v>
       </c>
       <c r="E5" t="n">
-        <v>1.045454545454546</v>
+        <v>1.039772727272727</v>
       </c>
       <c r="F5" t="n">
-        <v>72.43434343434343</v>
+        <v>72.38068181818181</v>
       </c>
       <c r="G5" t="n">
-        <v>4593939.393939395</v>
+        <v>4611931.818181818</v>
       </c>
       <c r="H5" t="n">
-        <v>76.40909090909092</v>
+        <v>76.28977272727273</v>
       </c>
       <c r="I5" t="n">
-        <v>25.09649122807018</v>
+        <v>25.43011363636364</v>
       </c>
       <c r="J5" t="n">
-        <v>182.9666666666666</v>
+        <v>183.9176136363636</v>
       </c>
       <c r="K5" t="n">
-        <v>1.285964912280702</v>
+        <v>1.35625</v>
       </c>
       <c r="L5" t="n">
-        <v>73.67660818713449</v>
+        <v>73.73693181818182</v>
       </c>
       <c r="M5" t="n">
-        <v>8849298.245614035</v>
+        <v>7957500</v>
       </c>
       <c r="N5" t="n">
-        <v>78.68654970760232</v>
+        <v>78.09261363636364</v>
       </c>
       <c r="O5" t="n">
-        <v>25.40753875753876</v>
+        <v>25.25982563380661</v>
       </c>
       <c r="P5" t="n">
-        <v>183.3722598389265</v>
+        <v>182.8208103038266</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.168166607055496</v>
+        <v>1.161642315514598</v>
       </c>
       <c r="R5" t="n">
-        <v>69.21181534514868</v>
+        <v>69.91994422395237</v>
       </c>
       <c r="S5" t="n">
-        <v>2532675.91307869</v>
+        <v>2831504.159902598</v>
       </c>
       <c r="T5" t="n">
-        <v>73.73546504935393</v>
+        <v>74.41547389305542</v>
       </c>
       <c r="U5" t="n">
-        <v>25.43478395746131</v>
+        <v>25.25337394813735</v>
       </c>
       <c r="V5" t="n">
-        <v>182.9528915994591</v>
+        <v>182.7666355829259</v>
       </c>
       <c r="W5" t="n">
-        <v>1.232163582667015</v>
+        <v>1.238638795109466</v>
       </c>
       <c r="X5" t="n">
-        <v>70.7764393598604</v>
+        <v>71.17697368444136</v>
       </c>
       <c r="Y5" t="n">
-        <v>3598983.947074622</v>
+        <v>4022459.930200689</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.08541191243708</v>
+        <v>76.73910066181804</v>
       </c>
     </row>
     <row r="6">
@@ -869,76 +893,76 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.52727272727272</v>
+        <v>24.50267379679144</v>
       </c>
       <c r="D6" t="n">
-        <v>185.2590909090909</v>
+        <v>185.3529411764706</v>
       </c>
       <c r="E6" t="n">
-        <v>1.277272727272728</v>
+        <v>1.283422459893048</v>
       </c>
       <c r="F6" t="n">
-        <v>75.24090909090908</v>
+        <v>75.51336898395722</v>
       </c>
       <c r="G6" t="n">
-        <v>11404204.54545455</v>
+        <v>12267647.05882353</v>
       </c>
       <c r="H6" t="n">
-        <v>79.9409090909091</v>
+        <v>80.08556149732621</v>
       </c>
       <c r="I6" t="n">
-        <v>25.1010101010101</v>
+        <v>25.01704545454545</v>
       </c>
       <c r="J6" t="n">
-        <v>186.4393939393939</v>
+        <v>186.5568181818182</v>
       </c>
       <c r="K6" t="n">
-        <v>1.050505050505051</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="L6" t="n">
-        <v>73.2929292929293</v>
+        <v>73.23863636363636</v>
       </c>
       <c r="M6" t="n">
-        <v>5193434.343434344</v>
+        <v>5014772.727272727</v>
       </c>
       <c r="N6" t="n">
-        <v>77.22222222222223</v>
+        <v>77.01136363636363</v>
       </c>
       <c r="O6" t="n">
-        <v>23.17949529844357</v>
+        <v>23.31207926023342</v>
       </c>
       <c r="P6" t="n">
-        <v>185.153879513845</v>
+        <v>184.9216622994615</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.189672975172975</v>
+        <v>1.195436060070948</v>
       </c>
       <c r="R6" t="n">
-        <v>70.3836387029318</v>
+        <v>71.49482277320006</v>
       </c>
       <c r="S6" t="n">
-        <v>5934669.931441483</v>
+        <v>7080806.646118513</v>
       </c>
       <c r="T6" t="n">
-        <v>77.4097358777876</v>
+        <v>77.97766870909872</v>
       </c>
       <c r="U6" t="n">
-        <v>25.3698263567708</v>
+        <v>25.37884961035697</v>
       </c>
       <c r="V6" t="n">
-        <v>183.5453445114556</v>
+        <v>183.0324518931504</v>
       </c>
       <c r="W6" t="n">
-        <v>1.088193858610525</v>
+        <v>1.068791702578467</v>
       </c>
       <c r="X6" t="n">
-        <v>70.46529340515451</v>
+        <v>71.0619448484522</v>
       </c>
       <c r="Y6" t="n">
-        <v>3050955.941178164</v>
+        <v>3350950.734620771</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.75181527834305</v>
+        <v>74.96703823409706</v>
       </c>
     </row>
     <row r="7">
@@ -951,76 +975,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.11004784688996</v>
+        <v>25.08522727272727</v>
       </c>
       <c r="D7" t="n">
-        <v>184.1387559808612</v>
+        <v>184.1647727272727</v>
       </c>
       <c r="E7" t="n">
-        <v>1.15311004784689</v>
+        <v>1.147727272727273</v>
       </c>
       <c r="F7" t="n">
-        <v>73.01435406698565</v>
+        <v>73.20454545454545</v>
       </c>
       <c r="G7" t="n">
-        <v>4804665.071770336</v>
+        <v>4914062.5</v>
       </c>
       <c r="H7" t="n">
-        <v>76.62200956937799</v>
+        <v>76.71590909090909</v>
       </c>
       <c r="I7" t="n">
-        <v>26.87727272727273</v>
+        <v>26.40588235294118</v>
       </c>
       <c r="J7" t="n">
-        <v>181.7954545454546</v>
+        <v>181.8941176470588</v>
       </c>
       <c r="K7" t="n">
-        <v>1.745454545454545</v>
+        <v>1.721925133689839</v>
       </c>
       <c r="L7" t="n">
-        <v>80.25</v>
+        <v>80.77593582887701</v>
       </c>
       <c r="M7" t="n">
-        <v>32505909.09090909</v>
+        <v>35282459.89304812</v>
       </c>
       <c r="N7" t="n">
-        <v>82</v>
+        <v>82.47647058823529</v>
       </c>
       <c r="O7" t="n">
-        <v>23.88974665685192</v>
+        <v>24.14795037138787</v>
       </c>
       <c r="P7" t="n">
-        <v>183.3524330445383</v>
+        <v>182.896041921042</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.024993038150933</v>
+        <v>1.031994047619048</v>
       </c>
       <c r="R7" t="n">
-        <v>69.73448091869145</v>
+        <v>70.53455051892551</v>
       </c>
       <c r="S7" t="n">
-        <v>2936683.328854382</v>
+        <v>3296554.26460114</v>
       </c>
       <c r="T7" t="n">
-        <v>74.98771408902988</v>
+        <v>75.27486581705331</v>
       </c>
       <c r="U7" t="n">
-        <v>25.26171777053356</v>
+        <v>25.13048875479437</v>
       </c>
       <c r="V7" t="n">
-        <v>182.1137667035694</v>
+        <v>180.9187551847348</v>
       </c>
       <c r="W7" t="n">
-        <v>1.542319873109347</v>
+        <v>1.588658208500044</v>
       </c>
       <c r="X7" t="n">
-        <v>75.27106461034093</v>
+        <v>76.11886165408519</v>
       </c>
       <c r="Y7" t="n">
-        <v>13390042.93531761</v>
+        <v>15461897.2773681</v>
       </c>
       <c r="Z7" t="n">
-        <v>78.81953215644005</v>
+        <v>79.30405093073888</v>
       </c>
     </row>
     <row r="8">
@@ -1033,76 +1057,76 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.80808080808081</v>
+        <v>25.71590909090909</v>
       </c>
       <c r="D8" t="n">
-        <v>184.4949494949495</v>
+        <v>184.4261363636363</v>
       </c>
       <c r="E8" t="n">
-        <v>1.257575757575758</v>
+        <v>1.255681818181818</v>
       </c>
       <c r="F8" t="n">
-        <v>72.24747474747475</v>
+        <v>72.30681818181819</v>
       </c>
       <c r="G8" t="n">
-        <v>3544949.494949495</v>
+        <v>3672159.090909091</v>
       </c>
       <c r="H8" t="n">
-        <v>75.46969696969697</v>
+        <v>75.59090909090909</v>
       </c>
       <c r="I8" t="n">
-        <v>26.84736842105263</v>
+        <v>26.80454545454545</v>
       </c>
       <c r="J8" t="n">
-        <v>182.474269005848</v>
+        <v>183.00625</v>
       </c>
       <c r="K8" t="n">
-        <v>2.259649122807018</v>
+        <v>2.241477272727272</v>
       </c>
       <c r="L8" t="n">
-        <v>78.67368421052633</v>
+        <v>79.00965909090908</v>
       </c>
       <c r="M8" t="n">
-        <v>21076081.87134503</v>
+        <v>22312159.09090909</v>
       </c>
       <c r="N8" t="n">
-        <v>80.54210526315791</v>
+        <v>80.66079545454545</v>
       </c>
       <c r="O8" t="n">
-        <v>25.81022706539948</v>
+        <v>26.06799560193957</v>
       </c>
       <c r="P8" t="n">
-        <v>183.757651575755</v>
+        <v>183.2890014718678</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.128747657195933</v>
+        <v>1.172249238628549</v>
       </c>
       <c r="R8" t="n">
-        <v>69.98425444287513</v>
+        <v>70.40985590080419</v>
       </c>
       <c r="S8" t="n">
-        <v>2639623.334519886</v>
+        <v>2738662.492061738</v>
       </c>
       <c r="T8" t="n">
-        <v>74.31963154980397</v>
+        <v>74.30863840820737</v>
       </c>
       <c r="U8" t="n">
-        <v>24.81503405581445</v>
+        <v>25.1649596771364</v>
       </c>
       <c r="V8" t="n">
-        <v>182.5881161666189</v>
+        <v>182.5540512110016</v>
       </c>
       <c r="W8" t="n">
-        <v>1.87133231962633</v>
+        <v>1.93875424543528</v>
       </c>
       <c r="X8" t="n">
-        <v>74.82057456994843</v>
+        <v>76.14382067684869</v>
       </c>
       <c r="Y8" t="n">
-        <v>13803595.86864033</v>
+        <v>16244290.40049191</v>
       </c>
       <c r="Z8" t="n">
-        <v>80.25960823373708</v>
+        <v>80.56642726885184</v>
       </c>
     </row>
     <row r="9">
@@ -1115,53 +1139,77 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>27.22683982683983</v>
+        <v>27.00983519404572</v>
       </c>
       <c r="D9" t="n">
-        <v>182.9428571428572</v>
+        <v>183.748591174907</v>
       </c>
       <c r="E9" t="n">
-        <v>1.868398268398268</v>
+        <v>1.771451355661882</v>
       </c>
       <c r="F9" t="n">
-        <v>78.24761904761904</v>
+        <v>77.9136629452419</v>
       </c>
       <c r="G9" t="n">
-        <v>19695584.41558442</v>
+        <v>18644630.51568315</v>
       </c>
       <c r="H9" t="n">
-        <v>80.15454545454547</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>80.03056884635834</v>
+      </c>
+      <c r="I9" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="J9" t="n">
+        <v>184.6772727272727</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2789659.090909091</v>
+      </c>
+      <c r="N9" t="n">
+        <v>74.65909090909091</v>
+      </c>
       <c r="O9" t="n">
-        <v>25.80220522173938</v>
+        <v>26.30585867623083</v>
       </c>
       <c r="P9" t="n">
-        <v>181.8394692735376</v>
+        <v>182.0373385877842</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.680378480502704</v>
+        <v>1.804168915110743</v>
       </c>
       <c r="R9" t="n">
-        <v>74.5140993857764</v>
+        <v>76.34267373933758</v>
       </c>
       <c r="S9" t="n">
-        <v>13875644.45823902</v>
+        <v>15912681.51152446</v>
       </c>
       <c r="T9" t="n">
-        <v>78.35601894424876</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+        <v>79.57422905088809</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.88763636363636</v>
+      </c>
+      <c r="V9" t="n">
+        <v>181.2584195804196</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.041741258741259</v>
+      </c>
+      <c r="X9" t="n">
+        <v>67.43983216783218</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1614444.055944056</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>72.04871328671328</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1173,76 +1221,76 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>24.2822966507177</v>
+        <v>24.22159090909091</v>
       </c>
       <c r="D10" t="n">
-        <v>184.2344497607655</v>
+        <v>184.1534090909091</v>
       </c>
       <c r="E10" t="n">
-        <v>1.00956937799043</v>
+        <v>1.005681818181818</v>
       </c>
       <c r="F10" t="n">
-        <v>72.19617224880383</v>
+        <v>72.36931818181819</v>
       </c>
       <c r="G10" t="n">
-        <v>5071531.100478468</v>
+        <v>5475852.272727272</v>
       </c>
       <c r="H10" t="n">
-        <v>77.51674641148327</v>
+        <v>77.58522727272728</v>
       </c>
       <c r="I10" t="n">
-        <v>25.56459330143541</v>
+        <v>25.72</v>
       </c>
       <c r="J10" t="n">
-        <v>187.1961722488038</v>
+        <v>187.4404545454545</v>
       </c>
       <c r="K10" t="n">
-        <v>1.492822966507177</v>
+        <v>1.515454545454545</v>
       </c>
       <c r="L10" t="n">
-        <v>78.26315789473684</v>
+        <v>78.34818181818181</v>
       </c>
       <c r="M10" t="n">
-        <v>19310287.08133971</v>
+        <v>19184318.18181818</v>
       </c>
       <c r="N10" t="n">
-        <v>81.83253588516747</v>
+        <v>81.74727272727273</v>
       </c>
       <c r="O10" t="n">
-        <v>23.0853502104303</v>
+        <v>23.35280784432958</v>
       </c>
       <c r="P10" t="n">
-        <v>182.9018937126946</v>
+        <v>182.5792163271511</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.077260405498392</v>
+        <v>1.090904150197628</v>
       </c>
       <c r="R10" t="n">
-        <v>67.42196572306412</v>
+        <v>68.50065863484342</v>
       </c>
       <c r="S10" t="n">
-        <v>2433707.509881423</v>
+        <v>2733771.359075707</v>
       </c>
       <c r="T10" t="n">
-        <v>74.63821286265221</v>
+        <v>75.15931210094254</v>
       </c>
       <c r="U10" t="n">
-        <v>25.89604615657247</v>
+        <v>25.61432364495408</v>
       </c>
       <c r="V10" t="n">
-        <v>186.6926368271105</v>
+        <v>186.6529753909537</v>
       </c>
       <c r="W10" t="n">
-        <v>1.406213484371379</v>
+        <v>1.416610934958761</v>
       </c>
       <c r="X10" t="n">
-        <v>74.59795887348518</v>
+        <v>75.16742954469041</v>
       </c>
       <c r="Y10" t="n">
-        <v>12306264.27738928</v>
+        <v>13296373.77320546</v>
       </c>
       <c r="Z10" t="n">
-        <v>78.42471789419157</v>
+        <v>78.97318542648978</v>
       </c>
     </row>
     <row r="11">
@@ -1255,53 +1303,77 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>25.64508240297714</v>
+        <v>25.80065124933546</v>
       </c>
       <c r="D11" t="n">
-        <v>185.8693248272195</v>
+        <v>186.4420919723551</v>
       </c>
       <c r="E11" t="n">
-        <v>1.892729930887825</v>
+        <v>1.809688995215311</v>
       </c>
       <c r="F11" t="n">
-        <v>80.73540669856459</v>
+        <v>80.37547846889952</v>
       </c>
       <c r="G11" t="n">
-        <v>31045049.17597023</v>
+        <v>29706951.08984582</v>
       </c>
       <c r="H11" t="n">
-        <v>84.19424508240297</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>83.93491493886232</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26.09488636363636</v>
+      </c>
+      <c r="J11" t="n">
+        <v>182.0313131313131</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.092550505050505</v>
+      </c>
+      <c r="L11" t="n">
+        <v>71.28573232323234</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3390509.785353535</v>
+      </c>
+      <c r="N11" t="n">
+        <v>73.5072601010101</v>
+      </c>
       <c r="O11" t="n">
-        <v>24.42791990985716</v>
+        <v>24.59595455510005</v>
       </c>
       <c r="P11" t="n">
-        <v>184.2685344133164</v>
+        <v>183.7342937296087</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.639830028924332</v>
+        <v>1.732917092676216</v>
       </c>
       <c r="R11" t="n">
-        <v>74.91975179262906</v>
+        <v>75.57961849791249</v>
       </c>
       <c r="S11" t="n">
-        <v>14242823.83156073</v>
+        <v>14379449.33362635</v>
       </c>
       <c r="T11" t="n">
-        <v>80.92671915382383</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+        <v>81.34020879377557</v>
+      </c>
+      <c r="U11" t="n">
+        <v>25.53798662278921</v>
+      </c>
+      <c r="V11" t="n">
+        <v>182.9264350690574</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.187009844257287</v>
+      </c>
+      <c r="X11" t="n">
+        <v>68.93913274660477</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2350843.943674878</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>72.42308060436177</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1441,53 +1513,77 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>25.65909090909091</v>
+        <v>25.55026737967914</v>
       </c>
       <c r="D16" t="n">
-        <v>185.7545454545455</v>
+        <v>186.6604278074867</v>
       </c>
       <c r="E16" t="n">
-        <v>1.186363636363637</v>
+        <v>1.187700534759358</v>
       </c>
       <c r="F16" t="n">
-        <v>73.7409090909091</v>
+        <v>73.5529411764706</v>
       </c>
       <c r="G16" t="n">
-        <v>6301590.909090909</v>
+        <v>5926871.657754011</v>
       </c>
       <c r="H16" t="n">
-        <v>77.56363636363636</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+        <v>77.51925133689839</v>
+      </c>
+      <c r="I16" t="n">
+        <v>26.12897727272728</v>
+      </c>
+      <c r="J16" t="n">
+        <v>184.0391414141414</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>66.85138888888889</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1185452.967171717</v>
+      </c>
+      <c r="N16" t="n">
+        <v>69.99785353535353</v>
+      </c>
       <c r="O16" t="n">
-        <v>24.85683886994232</v>
+        <v>24.50582693175426</v>
       </c>
       <c r="P16" t="n">
-        <v>184.4361339793667</v>
+        <v>184.9363906840303</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.138439585637862</v>
+        <v>1.145053993867822</v>
       </c>
       <c r="R16" t="n">
-        <v>70.6468399735641</v>
+        <v>71.03316229230067</v>
       </c>
       <c r="S16" t="n">
-        <v>3809298.473238128</v>
+        <v>4184631.048136781</v>
       </c>
       <c r="T16" t="n">
-        <v>76.88788009882838</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+        <v>77.17398527429526</v>
+      </c>
+      <c r="U16" t="n">
+        <v>24.87265791575574</v>
+      </c>
+      <c r="V16" t="n">
+        <v>183.4896629849619</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>64.88296396990691</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1058988.863883701</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>69.34134413593652</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1499,53 +1595,77 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>26.2555023923445</v>
+        <v>26.29772727272727</v>
       </c>
       <c r="D17" t="n">
-        <v>184.1397129186603</v>
+        <v>184.0636363636364</v>
       </c>
       <c r="E17" t="n">
-        <v>1.195215311004785</v>
+        <v>1.192045454545455</v>
       </c>
       <c r="F17" t="n">
-        <v>73.31961722488037</v>
+        <v>73.4465909090909</v>
       </c>
       <c r="G17" t="n">
-        <v>6612428.229665072</v>
+        <v>6644872.159090909</v>
       </c>
       <c r="H17" t="n">
-        <v>77.64114832535886</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>77.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>26.04772727272727</v>
+      </c>
+      <c r="J17" t="n">
+        <v>184.8403409090909</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>65.97727272727273</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1178267.045454545</v>
+      </c>
+      <c r="N17" t="n">
+        <v>69.29375</v>
+      </c>
       <c r="O17" t="n">
-        <v>26.10906278963554</v>
+        <v>26.65860588553603</v>
       </c>
       <c r="P17" t="n">
-        <v>184.8216194331984</v>
+        <v>184.5409919883357</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.359484803122574</v>
+        <v>1.39986415715276</v>
       </c>
       <c r="R17" t="n">
-        <v>69.48319841149564</v>
+        <v>70.64037415913336</v>
       </c>
       <c r="S17" t="n">
-        <v>3263790.357217602</v>
+        <v>3742602.524832534</v>
       </c>
       <c r="T17" t="n">
-        <v>73.75155994160639</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+        <v>74.10767259429025</v>
+      </c>
+      <c r="U17" t="n">
+        <v>26.03236695621207</v>
+      </c>
+      <c r="V17" t="n">
+        <v>182.606010776663</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>64.42874415489905</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1062892.325305029</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>68.1845579013378</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1557,53 +1677,77 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25.09649122807018</v>
+        <v>25.43011363636364</v>
       </c>
       <c r="D18" t="n">
-        <v>182.9666666666666</v>
+        <v>183.9176136363636</v>
       </c>
       <c r="E18" t="n">
-        <v>1.285964912280702</v>
+        <v>1.35625</v>
       </c>
       <c r="F18" t="n">
-        <v>73.67660818713449</v>
+        <v>73.73693181818182</v>
       </c>
       <c r="G18" t="n">
-        <v>8849298.245614035</v>
+        <v>7957500</v>
       </c>
       <c r="H18" t="n">
-        <v>78.68654970760232</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>78.09261363636364</v>
+      </c>
+      <c r="I18" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="J18" t="n">
+        <v>183.7528409090909</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.147727272727273</v>
+      </c>
+      <c r="L18" t="n">
+        <v>67.9153409090909</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1070465.909090909</v>
+      </c>
+      <c r="N18" t="n">
+        <v>70.03011363636364</v>
+      </c>
       <c r="O18" t="n">
-        <v>25.43478395746131</v>
+        <v>25.25337394813735</v>
       </c>
       <c r="P18" t="n">
-        <v>182.9528915994591</v>
+        <v>182.7666355829259</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.232163582667015</v>
+        <v>1.238638795109466</v>
       </c>
       <c r="R18" t="n">
-        <v>70.7764393598604</v>
+        <v>71.17697368444136</v>
       </c>
       <c r="S18" t="n">
-        <v>3598983.947074622</v>
+        <v>4022459.930200689</v>
       </c>
       <c r="T18" t="n">
-        <v>76.08541191243708</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+        <v>76.73910066181804</v>
+      </c>
+      <c r="U18" t="n">
+        <v>25.20870246299594</v>
+      </c>
+      <c r="V18" t="n">
+        <v>184.9972915610959</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.045622275771732</v>
+      </c>
+      <c r="X18" t="n">
+        <v>65.18824455536412</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>987446.7169027631</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>68.72725022964153</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1611,31 +1755,81 @@
           <t>bs5ow5pA</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>26.82929292929293</v>
+      </c>
+      <c r="D19" t="n">
+        <v>185.6604545454546</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.075909090909091</v>
+      </c>
+      <c r="F19" t="n">
+        <v>69.71712121212121</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2019979.797979798</v>
+      </c>
+      <c r="H19" t="n">
+        <v>73.00373737373738</v>
+      </c>
+      <c r="I19" t="n">
+        <v>27.71139169472503</v>
+      </c>
+      <c r="J19" t="n">
+        <v>181.6445005611672</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.043434343434343</v>
+      </c>
+      <c r="L19" t="n">
+        <v>67.66812570145903</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1479500</v>
+      </c>
+      <c r="N19" t="n">
+        <v>70.08355780022447</v>
+      </c>
+      <c r="O19" t="n">
+        <v>26.98757034632035</v>
+      </c>
+      <c r="P19" t="n">
+        <v>185.3590241624318</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.133275574063617</v>
+      </c>
+      <c r="R19" t="n">
+        <v>69.62046988518728</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2075383.015716168</v>
+      </c>
+      <c r="T19" t="n">
+        <v>73.06944939299831</v>
+      </c>
+      <c r="U19" t="n">
+        <v>25.51145559775422</v>
+      </c>
+      <c r="V19" t="n">
+        <v>178.8296919630501</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.039837852206273</v>
+      </c>
+      <c r="X19" t="n">
+        <v>65.12262567883849</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1192660.187378094</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>69.31615173770209</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1647,53 +1841,77 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>25.2979797979798</v>
+        <v>25.26704545454545</v>
       </c>
       <c r="D20" t="n">
-        <v>183.8989898989899</v>
+        <v>183.9318181818182</v>
       </c>
       <c r="E20" t="n">
-        <v>1.045454545454546</v>
+        <v>1.039772727272727</v>
       </c>
       <c r="F20" t="n">
-        <v>72.43434343434343</v>
+        <v>72.38068181818181</v>
       </c>
       <c r="G20" t="n">
-        <v>4593939.393939395</v>
+        <v>4611931.818181818</v>
       </c>
       <c r="H20" t="n">
-        <v>76.40909090909092</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>76.28977272727273</v>
+      </c>
+      <c r="I20" t="n">
+        <v>26.84976076555024</v>
+      </c>
+      <c r="J20" t="n">
+        <v>181.4129186602871</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>67.53779904306221</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1317033.492822966</v>
+      </c>
+      <c r="N20" t="n">
+        <v>70.63827751196173</v>
+      </c>
       <c r="O20" t="n">
-        <v>25.40753875753876</v>
+        <v>25.25982563380661</v>
       </c>
       <c r="P20" t="n">
-        <v>183.3722598389265</v>
+        <v>182.8208103038266</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.168166607055496</v>
+        <v>1.161642315514598</v>
       </c>
       <c r="R20" t="n">
-        <v>69.21181534514868</v>
+        <v>69.91994422395237</v>
       </c>
       <c r="S20" t="n">
-        <v>2532675.91307869</v>
+        <v>2831504.159902598</v>
       </c>
       <c r="T20" t="n">
-        <v>73.73546504935393</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+        <v>74.41547389305542</v>
+      </c>
+      <c r="U20" t="n">
+        <v>25.28923867216773</v>
+      </c>
+      <c r="V20" t="n">
+        <v>179.4360243633813</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>66.08823967540215</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1242947.921008562</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>71.20271346671805</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1705,53 +1923,77 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>26.87727272727273</v>
+        <v>26.40588235294118</v>
       </c>
       <c r="D21" t="n">
-        <v>181.7954545454546</v>
+        <v>181.8941176470588</v>
       </c>
       <c r="E21" t="n">
-        <v>1.745454545454545</v>
+        <v>1.721925133689839</v>
       </c>
       <c r="F21" t="n">
-        <v>80.25</v>
+        <v>80.77593582887701</v>
       </c>
       <c r="G21" t="n">
-        <v>32505909.09090909</v>
+        <v>35282459.89304812</v>
       </c>
       <c r="H21" t="n">
-        <v>82</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+        <v>82.47647058823529</v>
+      </c>
+      <c r="I21" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="J21" t="n">
+        <v>184.2102272727273</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>66.59090909090909</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1288068.181818182</v>
+      </c>
+      <c r="N21" t="n">
+        <v>70.38636363636363</v>
+      </c>
       <c r="O21" t="n">
-        <v>25.26171777053356</v>
+        <v>25.13048875479437</v>
       </c>
       <c r="P21" t="n">
-        <v>182.1137667035694</v>
+        <v>180.9187551847348</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.542319873109347</v>
+        <v>1.588658208500044</v>
       </c>
       <c r="R21" t="n">
-        <v>75.27106461034093</v>
+        <v>76.11886165408519</v>
       </c>
       <c r="S21" t="n">
-        <v>13390042.93531761</v>
+        <v>15461897.2773681</v>
       </c>
       <c r="T21" t="n">
-        <v>78.81953215644005</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+        <v>79.30405093073888</v>
+      </c>
+      <c r="U21" t="n">
+        <v>24.86031760793131</v>
+      </c>
+      <c r="V21" t="n">
+        <v>183.1438840745184</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>64.69860750180831</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1074530.059269408</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>69.90788450666525</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1759,31 +2001,81 @@
           <t>6sP22LDL</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>25.38983957219251</v>
+      </c>
+      <c r="D22" t="n">
+        <v>182.8754010695187</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>66.74171122994652</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1330446.524064171</v>
+      </c>
+      <c r="H22" t="n">
+        <v>70.87700534759358</v>
+      </c>
+      <c r="I22" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="J22" t="n">
+        <v>184.6772727272727</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2789659.090909091</v>
+      </c>
+      <c r="N22" t="n">
+        <v>74.65909090909091</v>
+      </c>
+      <c r="O22" t="n">
+        <v>23.96401371066244</v>
+      </c>
+      <c r="P22" t="n">
+        <v>182.7557862196891</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>64.26416148906799</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1148810.962755532</v>
+      </c>
+      <c r="T22" t="n">
+        <v>70.60957445485401</v>
+      </c>
+      <c r="U22" t="n">
+        <v>25.88763636363636</v>
+      </c>
+      <c r="V22" t="n">
+        <v>181.2584195804196</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.041741258741259</v>
+      </c>
+      <c r="X22" t="n">
+        <v>67.43983216783218</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1614444.055944056</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>72.04871328671328</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1791,31 +2083,81 @@
           <t>bepKi4a3</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>24.83522727272727</v>
+      </c>
+      <c r="D23" t="n">
+        <v>185.2846590909091</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.048295454545455</v>
+      </c>
+      <c r="F23" t="n">
+        <v>70.28352272727273</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3159488.636363637</v>
+      </c>
+      <c r="H23" t="n">
+        <v>75.71704545454546</v>
+      </c>
+      <c r="I23" t="n">
+        <v>26.05741626794259</v>
+      </c>
+      <c r="J23" t="n">
+        <v>182.6842105263158</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>70.47368421052632</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2572368.421052631</v>
+      </c>
+      <c r="N23" t="n">
+        <v>74.23444976076556</v>
+      </c>
+      <c r="O23" t="n">
+        <v>24.6143007556051</v>
+      </c>
+      <c r="P23" t="n">
+        <v>184.460542665366</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.093067748978075</v>
+      </c>
+      <c r="R23" t="n">
+        <v>68.31454288213799</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2369897.367188468</v>
+      </c>
+      <c r="T23" t="n">
+        <v>73.64909265452744</v>
+      </c>
+      <c r="U23" t="n">
+        <v>25.21937256742749</v>
+      </c>
+      <c r="V23" t="n">
+        <v>182.5511065148937</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>68.28994341111044</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1967047.142195883</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>73.30714222848091</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1823,31 +2165,81 @@
           <t>ILr8tvi2</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>23.51336898395722</v>
+      </c>
+      <c r="D24" t="n">
+        <v>184.3983957219251</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.119786096256685</v>
+      </c>
+      <c r="F24" t="n">
+        <v>68.04278074866309</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2179572.192513369</v>
+      </c>
+      <c r="H24" t="n">
+        <v>75.11764705882354</v>
+      </c>
+      <c r="I24" t="n">
+        <v>26.09488636363636</v>
+      </c>
+      <c r="J24" t="n">
+        <v>182.0313131313131</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.092550505050505</v>
+      </c>
+      <c r="L24" t="n">
+        <v>71.28573232323234</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3390509.785353535</v>
+      </c>
+      <c r="N24" t="n">
+        <v>73.5072601010101</v>
+      </c>
+      <c r="O24" t="n">
+        <v>24.17799173248466</v>
+      </c>
+      <c r="P24" t="n">
+        <v>183.1683435468368</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.118994413451153</v>
+      </c>
+      <c r="R24" t="n">
+        <v>67.5497590991599</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2264739.295663167</v>
+      </c>
+      <c r="T24" t="n">
+        <v>74.15072340261564</v>
+      </c>
+      <c r="U24" t="n">
+        <v>25.53798662278921</v>
+      </c>
+      <c r="V24" t="n">
+        <v>182.9264350690574</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.187009844257287</v>
+      </c>
+      <c r="X24" t="n">
+        <v>68.93913274660477</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2350843.943674878</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>72.42308060436177</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1859,53 +2251,77 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>26.13540669856459</v>
+        <v>25.89946524064171</v>
       </c>
       <c r="D25" t="n">
-        <v>186.2177033492823</v>
+        <v>186.2572192513369</v>
       </c>
       <c r="E25" t="n">
-        <v>1.345933014354067</v>
+        <v>1.275935828877006</v>
       </c>
       <c r="F25" t="n">
-        <v>75.70526315789475</v>
+        <v>75.78983957219252</v>
       </c>
       <c r="G25" t="n">
-        <v>11967655.50239235</v>
+        <v>12650855.61497326</v>
       </c>
       <c r="H25" t="n">
-        <v>78.98373205741628</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+        <v>79.04010695187166</v>
+      </c>
+      <c r="I25" t="n">
+        <v>25.96022727272727</v>
+      </c>
+      <c r="J25" t="n">
+        <v>182.1534090909091</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>67.96590909090909</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1431676.136363636</v>
+      </c>
+      <c r="N25" t="n">
+        <v>71.3125</v>
+      </c>
       <c r="O25" t="n">
-        <v>24.07371712892326</v>
+        <v>24.57152140523933</v>
       </c>
       <c r="P25" t="n">
-        <v>186.2325411991373</v>
+        <v>185.391205899366</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.176680160858098</v>
+        <v>1.16637106491948</v>
       </c>
       <c r="R25" t="n">
-        <v>70.70015071335341</v>
+        <v>72.04009418022972</v>
       </c>
       <c r="S25" t="n">
-        <v>4672714.393404471</v>
+        <v>6506192.078869222</v>
       </c>
       <c r="T25" t="n">
-        <v>76.29963134334571</v>
-      </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+        <v>76.63134153362353</v>
+      </c>
+      <c r="U25" t="n">
+        <v>24.20298770171053</v>
+      </c>
+      <c r="V25" t="n">
+        <v>181.7787160578901</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>66.87255769108531</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1468977.295540743</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>72.89249775226892</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1917,53 +2333,77 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>23.89665071770335</v>
+        <v>23.85227272727273</v>
       </c>
       <c r="D26" t="n">
-        <v>184.5736842105263</v>
+        <v>184.9125</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>70.6645933014354</v>
+        <v>70.99431818181819</v>
       </c>
       <c r="G26" t="n">
-        <v>3936411.483253589</v>
+        <v>4426576.704545455</v>
       </c>
       <c r="H26" t="n">
-        <v>76.43540669856458</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+        <v>76.73238636363635</v>
+      </c>
+      <c r="I26" t="n">
+        <v>25.65738636363636</v>
+      </c>
+      <c r="J26" t="n">
+        <v>182.9284090909091</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.048863636363636</v>
+      </c>
+      <c r="L26" t="n">
+        <v>67.19374999999999</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1440724.431818182</v>
+      </c>
+      <c r="N26" t="n">
+        <v>71.80397727272727</v>
+      </c>
       <c r="O26" t="n">
-        <v>23.74312561203669</v>
+        <v>23.24593971797401</v>
       </c>
       <c r="P26" t="n">
-        <v>183.6335690322987</v>
+        <v>184.4125499888806</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>67.26407692462139</v>
+        <v>67.91933814500578</v>
       </c>
       <c r="S26" t="n">
-        <v>2169314.78978439</v>
+        <v>2648315.453954744</v>
       </c>
       <c r="T26" t="n">
-        <v>73.99388850042207</v>
-      </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+        <v>75.05871282201821</v>
+      </c>
+      <c r="U26" t="n">
+        <v>26.64023610899969</v>
+      </c>
+      <c r="V26" t="n">
+        <v>181.6456480214632</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.136952686001599</v>
+      </c>
+      <c r="X26" t="n">
+        <v>66.7535016307163</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1326626.642698586</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>70.54761178887537</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1975,53 +2415,77 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>25.48011695906433</v>
+        <v>26.2530303030303</v>
       </c>
       <c r="D27" t="n">
-        <v>184.7134502923977</v>
+        <v>184.3292929292929</v>
       </c>
       <c r="E27" t="n">
-        <v>1.184795321637427</v>
+        <v>1.41155303030303</v>
       </c>
       <c r="F27" t="n">
-        <v>71.70877192982455</v>
+        <v>72.08440656565656</v>
       </c>
       <c r="G27" t="n">
-        <v>3679389.619883041</v>
+        <v>3591829.22979798</v>
       </c>
       <c r="H27" t="n">
-        <v>76.68830409356725</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+        <v>76.73301767676767</v>
+      </c>
+      <c r="I27" t="n">
+        <v>26.04895833333333</v>
+      </c>
+      <c r="J27" t="n">
+        <v>183.3173611111111</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.107986111111111</v>
+      </c>
+      <c r="L27" t="n">
+        <v>68.32361111111112</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1612200.520833333</v>
+      </c>
+      <c r="N27" t="n">
+        <v>72.12708333333333</v>
+      </c>
       <c r="O27" t="n">
-        <v>24.6741246188859</v>
+        <v>24.9311284544162</v>
       </c>
       <c r="P27" t="n">
-        <v>184.6261118048392</v>
+        <v>184.1562631711357</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.180213963430519</v>
+        <v>1.22161293970963</v>
       </c>
       <c r="R27" t="n">
-        <v>69.8347690796159</v>
+        <v>70.43439926510482</v>
       </c>
       <c r="S27" t="n">
-        <v>3509979.030992454</v>
+        <v>3692779.612421285</v>
       </c>
       <c r="T27" t="n">
-        <v>75.79803688833753</v>
-      </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+        <v>75.88315246645284</v>
+      </c>
+      <c r="U27" t="n">
+        <v>24.06148563210563</v>
+      </c>
+      <c r="V27" t="n">
+        <v>183.7574836970969</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>64.34535148497892</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1158894.516700286</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>70.7957318181199</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2029,31 +2493,81 @@
           <t>8KfYbJz0</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>25.38983957219251</v>
+      </c>
+      <c r="D28" t="n">
+        <v>182.8754010695187</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>66.74171122994652</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1330446.524064171</v>
+      </c>
+      <c r="H28" t="n">
+        <v>70.87700534759358</v>
+      </c>
+      <c r="I28" t="n">
+        <v>26.05741626794259</v>
+      </c>
+      <c r="J28" t="n">
+        <v>182.6842105263158</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>70.47368421052632</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2572368.421052631</v>
+      </c>
+      <c r="N28" t="n">
+        <v>74.23444976076556</v>
+      </c>
+      <c r="O28" t="n">
+        <v>23.96401371066244</v>
+      </c>
+      <c r="P28" t="n">
+        <v>182.7557862196891</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>64.26416148906799</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1148810.962755532</v>
+      </c>
+      <c r="T28" t="n">
+        <v>70.60957445485401</v>
+      </c>
+      <c r="U28" t="n">
+        <v>25.21937256742749</v>
+      </c>
+      <c r="V28" t="n">
+        <v>182.5511065148937</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>68.28994341111044</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1967047.142195883</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>73.30714222848091</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2061,25 +2575,51 @@
           <t>EL1P0u6m</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>27.71139169472503</v>
+      </c>
+      <c r="D29" t="n">
+        <v>181.6445005611672</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.043434343434343</v>
+      </c>
+      <c r="F29" t="n">
+        <v>67.66812570145903</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1479500</v>
+      </c>
+      <c r="H29" t="n">
+        <v>70.08355780022447</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>25.51145559775422</v>
+      </c>
+      <c r="P29" t="n">
+        <v>178.8296919630501</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.039837852206273</v>
+      </c>
+      <c r="R29" t="n">
+        <v>65.12262567883849</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1192660.187378094</v>
+      </c>
+      <c r="T29" t="n">
+        <v>69.31615173770209</v>
+      </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
@@ -2093,31 +2633,81 @@
           <t>M5TEBdK5</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>25.65738636363636</v>
+      </c>
+      <c r="D30" t="n">
+        <v>182.9284090909091</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.048863636363636</v>
+      </c>
+      <c r="F30" t="n">
+        <v>67.19374999999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1440724.431818182</v>
+      </c>
+      <c r="H30" t="n">
+        <v>71.80397727272727</v>
+      </c>
+      <c r="I30" t="n">
+        <v>26.04895833333333</v>
+      </c>
+      <c r="J30" t="n">
+        <v>183.3173611111111</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.107986111111111</v>
+      </c>
+      <c r="L30" t="n">
+        <v>68.32361111111112</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1612200.520833333</v>
+      </c>
+      <c r="N30" t="n">
+        <v>72.12708333333333</v>
+      </c>
+      <c r="O30" t="n">
+        <v>26.64023610899969</v>
+      </c>
+      <c r="P30" t="n">
+        <v>181.6456480214632</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.136952686001599</v>
+      </c>
+      <c r="R30" t="n">
+        <v>66.7535016307163</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1326626.642698586</v>
+      </c>
+      <c r="T30" t="n">
+        <v>70.54761178887537</v>
+      </c>
+      <c r="U30" t="n">
+        <v>24.06148563210563</v>
+      </c>
+      <c r="V30" t="n">
+        <v>183.7574836970969</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>64.34535148497892</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1158894.516700286</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>70.7957318181199</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2129,53 +2719,77 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>25.48011695906433</v>
+        <v>26.2530303030303</v>
       </c>
       <c r="D31" t="n">
-        <v>184.7134502923977</v>
+        <v>184.3292929292929</v>
       </c>
       <c r="E31" t="n">
-        <v>1.184795321637427</v>
+        <v>1.41155303030303</v>
       </c>
       <c r="F31" t="n">
-        <v>71.70877192982455</v>
+        <v>72.08440656565656</v>
       </c>
       <c r="G31" t="n">
-        <v>3679389.619883041</v>
+        <v>3591829.22979798</v>
       </c>
       <c r="H31" t="n">
-        <v>76.68830409356725</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+        <v>76.73301767676767</v>
+      </c>
+      <c r="I31" t="n">
+        <v>26.12897727272728</v>
+      </c>
+      <c r="J31" t="n">
+        <v>184.0391414141414</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>66.85138888888889</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1185452.967171717</v>
+      </c>
+      <c r="N31" t="n">
+        <v>69.99785353535353</v>
+      </c>
       <c r="O31" t="n">
-        <v>24.6741246188859</v>
+        <v>24.9311284544162</v>
       </c>
       <c r="P31" t="n">
-        <v>184.6261118048392</v>
+        <v>184.1562631711357</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.180213963430519</v>
+        <v>1.22161293970963</v>
       </c>
       <c r="R31" t="n">
-        <v>69.8347690796159</v>
+        <v>70.43439926510482</v>
       </c>
       <c r="S31" t="n">
-        <v>3509979.030992454</v>
+        <v>3692779.612421285</v>
       </c>
       <c r="T31" t="n">
-        <v>75.79803688833753</v>
-      </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
+        <v>75.88315246645284</v>
+      </c>
+      <c r="U31" t="n">
+        <v>24.87265791575574</v>
+      </c>
+      <c r="V31" t="n">
+        <v>183.4896629849619</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>64.88296396990691</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1058988.863883701</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>69.34134413593652</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2183,31 +2797,81 @@
           <t>WvwvCQVo</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="D32" t="n">
+        <v>183.7528409090909</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.147727272727273</v>
+      </c>
+      <c r="F32" t="n">
+        <v>67.9153409090909</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1070465.909090909</v>
+      </c>
+      <c r="H32" t="n">
+        <v>70.03011363636364</v>
+      </c>
+      <c r="I32" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="J32" t="n">
+        <v>184.2102272727273</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>66.59090909090909</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1288068.181818182</v>
+      </c>
+      <c r="N32" t="n">
+        <v>70.38636363636363</v>
+      </c>
+      <c r="O32" t="n">
+        <v>25.20870246299594</v>
+      </c>
+      <c r="P32" t="n">
+        <v>184.9972915610959</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.045622275771732</v>
+      </c>
+      <c r="R32" t="n">
+        <v>65.18824455536412</v>
+      </c>
+      <c r="S32" t="n">
+        <v>987446.7169027631</v>
+      </c>
+      <c r="T32" t="n">
+        <v>68.72725022964153</v>
+      </c>
+      <c r="U32" t="n">
+        <v>24.86031760793131</v>
+      </c>
+      <c r="V32" t="n">
+        <v>183.1438840745184</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>64.69860750180831</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1074530.059269408</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>69.90788450666525</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2218,53 +2882,77 @@
       <c r="B33" t="n">
         <v>1</v>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>26.84976076555024</v>
+      </c>
+      <c r="D33" t="n">
+        <v>181.4129186602871</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>67.53779904306221</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1317033.492822966</v>
+      </c>
+      <c r="H33" t="n">
+        <v>70.63827751196173</v>
+      </c>
       <c r="I33" t="n">
-        <v>25.65909090909091</v>
+        <v>25.55026737967914</v>
       </c>
       <c r="J33" t="n">
-        <v>185.7545454545455</v>
+        <v>186.6604278074867</v>
       </c>
       <c r="K33" t="n">
-        <v>1.186363636363637</v>
+        <v>1.187700534759358</v>
       </c>
       <c r="L33" t="n">
-        <v>73.7409090909091</v>
+        <v>73.5529411764706</v>
       </c>
       <c r="M33" t="n">
-        <v>6301590.909090909</v>
+        <v>5926871.657754011</v>
       </c>
       <c r="N33" t="n">
-        <v>77.56363636363636</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+        <v>77.51925133689839</v>
+      </c>
+      <c r="O33" t="n">
+        <v>25.28923867216773</v>
+      </c>
+      <c r="P33" t="n">
+        <v>179.4360243633813</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>66.08823967540215</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1242947.921008562</v>
+      </c>
+      <c r="T33" t="n">
+        <v>71.20271346671805</v>
+      </c>
       <c r="U33" t="n">
-        <v>24.85683886994232</v>
+        <v>24.50582693175426</v>
       </c>
       <c r="V33" t="n">
-        <v>184.4361339793667</v>
+        <v>184.9363906840303</v>
       </c>
       <c r="W33" t="n">
-        <v>1.138439585637862</v>
+        <v>1.145053993867822</v>
       </c>
       <c r="X33" t="n">
-        <v>70.6468399735641</v>
+        <v>71.03316229230067</v>
       </c>
       <c r="Y33" t="n">
-        <v>3809298.473238128</v>
+        <v>4184631.048136781</v>
       </c>
       <c r="Z33" t="n">
-        <v>76.88788009882838</v>
+        <v>77.17398527429526</v>
       </c>
     </row>
     <row r="34">
@@ -2305,31 +2993,81 @@
           <t>SORbFvLt</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>25.96022727272727</v>
+      </c>
+      <c r="D35" t="n">
+        <v>182.1534090909091</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>67.96590909090909</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1431676.136363636</v>
+      </c>
+      <c r="H35" t="n">
+        <v>71.3125</v>
+      </c>
+      <c r="I35" t="n">
+        <v>26.82929292929293</v>
+      </c>
+      <c r="J35" t="n">
+        <v>185.6604545454546</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.075909090909091</v>
+      </c>
+      <c r="L35" t="n">
+        <v>69.71712121212121</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2019979.797979798</v>
+      </c>
+      <c r="N35" t="n">
+        <v>73.00373737373738</v>
+      </c>
+      <c r="O35" t="n">
+        <v>24.20298770171053</v>
+      </c>
+      <c r="P35" t="n">
+        <v>181.7787160578901</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>66.87255769108531</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1468977.295540743</v>
+      </c>
+      <c r="T35" t="n">
+        <v>72.89249775226892</v>
+      </c>
+      <c r="U35" t="n">
+        <v>26.98757034632035</v>
+      </c>
+      <c r="V35" t="n">
+        <v>185.3590241624318</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.133275574063617</v>
+      </c>
+      <c r="X35" t="n">
+        <v>69.62046988518728</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2075383.015716168</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>73.06944939299831</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -2341,53 +3079,77 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>23.89665071770335</v>
+        <v>23.85227272727273</v>
       </c>
       <c r="D36" t="n">
-        <v>184.5736842105263</v>
+        <v>184.9125</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>70.6645933014354</v>
+        <v>70.99431818181819</v>
       </c>
       <c r="G36" t="n">
-        <v>3936411.483253589</v>
+        <v>4426576.704545455</v>
       </c>
       <c r="H36" t="n">
-        <v>76.43540669856458</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+        <v>76.73238636363635</v>
+      </c>
+      <c r="I36" t="n">
+        <v>23.51336898395722</v>
+      </c>
+      <c r="J36" t="n">
+        <v>184.3983957219251</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.119786096256685</v>
+      </c>
+      <c r="L36" t="n">
+        <v>68.04278074866309</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2179572.192513369</v>
+      </c>
+      <c r="N36" t="n">
+        <v>75.11764705882354</v>
+      </c>
       <c r="O36" t="n">
-        <v>23.74312561203669</v>
+        <v>23.24593971797401</v>
       </c>
       <c r="P36" t="n">
-        <v>183.6335690322987</v>
+        <v>184.4125499888806</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>67.26407692462139</v>
+        <v>67.91933814500578</v>
       </c>
       <c r="S36" t="n">
-        <v>2169314.78978439</v>
+        <v>2648315.453954744</v>
       </c>
       <c r="T36" t="n">
-        <v>73.99388850042207</v>
-      </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+        <v>75.05871282201821</v>
+      </c>
+      <c r="U36" t="n">
+        <v>24.17799173248466</v>
+      </c>
+      <c r="V36" t="n">
+        <v>183.1683435468368</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.118994413451153</v>
+      </c>
+      <c r="X36" t="n">
+        <v>67.5497590991599</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2264739.295663167</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>74.15072340261564</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -2395,25 +3157,51 @@
           <t>IXMN9zkI</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>26.04772727272727</v>
+      </c>
+      <c r="D37" t="n">
+        <v>184.8403409090909</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>65.97727272727273</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1178267.045454545</v>
+      </c>
+      <c r="H37" t="n">
+        <v>69.29375</v>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>26.03236695621207</v>
+      </c>
+      <c r="P37" t="n">
+        <v>182.606010776663</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>64.42874415489905</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1062892.325305029</v>
+      </c>
+      <c r="T37" t="n">
+        <v>68.1845579013378</v>
+      </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>

--- a/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -665,22 +665,22 @@
         <v>75.71704545454546</v>
       </c>
       <c r="I3" t="n">
-        <v>26.47272727272727</v>
+        <v>26.38787878787879</v>
       </c>
       <c r="J3" t="n">
-        <v>183.299043062201</v>
+        <v>183.3323232323232</v>
       </c>
       <c r="K3" t="n">
-        <v>1.659808612440191</v>
+        <v>1.674242424242424</v>
       </c>
       <c r="L3" t="n">
-        <v>76.55263157894737</v>
+        <v>76.55000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>12639234.44976077</v>
+        <v>12781414.14141414</v>
       </c>
       <c r="N3" t="n">
-        <v>79.59282296650717</v>
+        <v>79.64797979797979</v>
       </c>
       <c r="O3" t="n">
         <v>24.6143007556051</v>
@@ -701,22 +701,22 @@
         <v>73.64909265452744</v>
       </c>
       <c r="U3" t="n">
-        <v>25.18913312991139</v>
+        <v>25.21519608157313</v>
       </c>
       <c r="V3" t="n">
-        <v>181.7304426151949</v>
+        <v>181.6599116493724</v>
       </c>
       <c r="W3" t="n">
-        <v>1.555732653951453</v>
+        <v>1.546606690282089</v>
       </c>
       <c r="X3" t="n">
-        <v>74.66489422349525</v>
+        <v>74.63072168035612</v>
       </c>
       <c r="Y3" t="n">
-        <v>11666847.64528231</v>
+        <v>11503672.51446466</v>
       </c>
       <c r="Z3" t="n">
-        <v>79.10342347760094</v>
+        <v>79.02916922635656</v>
       </c>
     </row>
     <row r="4">
@@ -811,7 +811,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.26704545454545</v>
+        <v>25.26704545454546</v>
       </c>
       <c r="D5" t="n">
         <v>183.9318181818182</v>
@@ -859,7 +859,7 @@
         <v>69.91994422395237</v>
       </c>
       <c r="S5" t="n">
-        <v>2831504.159902598</v>
+        <v>2831504.159902597</v>
       </c>
       <c r="T5" t="n">
         <v>74.41547389305542</v>
@@ -941,7 +941,7 @@
         <v>71.49482277320006</v>
       </c>
       <c r="S6" t="n">
-        <v>7080806.646118513</v>
+        <v>7080806.646118512</v>
       </c>
       <c r="T6" t="n">
         <v>77.97766870909872</v>
@@ -1017,19 +1017,19 @@
         <v>182.896041921042</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.031994047619048</v>
+        <v>1.031994047619047</v>
       </c>
       <c r="R7" t="n">
         <v>70.53455051892551</v>
       </c>
       <c r="S7" t="n">
-        <v>3296554.26460114</v>
+        <v>3296554.264601139</v>
       </c>
       <c r="T7" t="n">
         <v>75.27486581705331</v>
       </c>
       <c r="U7" t="n">
-        <v>25.13048875479437</v>
+        <v>25.13048875479438</v>
       </c>
       <c r="V7" t="n">
         <v>180.9187551847348</v>
@@ -1096,7 +1096,7 @@
         <v>26.06799560193957</v>
       </c>
       <c r="P8" t="n">
-        <v>183.2890014718678</v>
+        <v>183.2890014718679</v>
       </c>
       <c r="Q8" t="n">
         <v>1.172249238628549</v>
@@ -1221,22 +1221,22 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>24.22159090909091</v>
+        <v>24.22424242424243</v>
       </c>
       <c r="D10" t="n">
-        <v>184.1534090909091</v>
+        <v>184.2242424242424</v>
       </c>
       <c r="E10" t="n">
-        <v>1.005681818181818</v>
+        <v>1.006060606060606</v>
       </c>
       <c r="F10" t="n">
-        <v>72.36931818181819</v>
+        <v>72.31515151515153</v>
       </c>
       <c r="G10" t="n">
-        <v>5475852.272727272</v>
+        <v>5439696.96969697</v>
       </c>
       <c r="H10" t="n">
-        <v>77.58522727272728</v>
+        <v>77.56363636363636</v>
       </c>
       <c r="I10" t="n">
         <v>25.72</v>
@@ -1257,22 +1257,22 @@
         <v>81.74727272727273</v>
       </c>
       <c r="O10" t="n">
-        <v>23.35280784432958</v>
+        <v>23.3850240194588</v>
       </c>
       <c r="P10" t="n">
-        <v>182.5792163271511</v>
+        <v>182.5975408938887</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.090904150197628</v>
+        <v>1.088268774703557</v>
       </c>
       <c r="R10" t="n">
-        <v>68.50065863484342</v>
+        <v>68.49635471774603</v>
       </c>
       <c r="S10" t="n">
-        <v>2733771.359075707</v>
+        <v>2727761.91344887</v>
       </c>
       <c r="T10" t="n">
-        <v>75.15931210094254</v>
+        <v>75.08297638593291</v>
       </c>
       <c r="U10" t="n">
         <v>25.61432364495408</v>
@@ -1552,7 +1552,7 @@
         <v>24.50582693175426</v>
       </c>
       <c r="P16" t="n">
-        <v>184.9363906840303</v>
+        <v>184.9363906840302</v>
       </c>
       <c r="Q16" t="n">
         <v>1.145053993867822</v>
@@ -1777,22 +1777,22 @@
         <v>73.00373737373738</v>
       </c>
       <c r="I19" t="n">
-        <v>27.71139169472503</v>
+        <v>27.7473559120618</v>
       </c>
       <c r="J19" t="n">
-        <v>181.6445005611672</v>
+        <v>181.5882947118241</v>
       </c>
       <c r="K19" t="n">
-        <v>1.043434343434343</v>
+        <v>1.034224598930481</v>
       </c>
       <c r="L19" t="n">
-        <v>67.66812570145903</v>
+        <v>67.67801544860369</v>
       </c>
       <c r="M19" t="n">
-        <v>1479500</v>
+        <v>1467750</v>
       </c>
       <c r="N19" t="n">
-        <v>70.08355780022447</v>
+        <v>70.06494355317885</v>
       </c>
       <c r="O19" t="n">
         <v>26.98757034632035</v>
@@ -1813,22 +1813,22 @@
         <v>73.06944939299831</v>
       </c>
       <c r="U19" t="n">
-        <v>25.51145559775422</v>
+        <v>25.55223640831731</v>
       </c>
       <c r="V19" t="n">
-        <v>178.8296919630501</v>
+        <v>178.8410642175611</v>
       </c>
       <c r="W19" t="n">
-        <v>1.039837852206273</v>
+        <v>1.036833661694343</v>
       </c>
       <c r="X19" t="n">
-        <v>65.12262567883849</v>
+        <v>65.21807424818194</v>
       </c>
       <c r="Y19" t="n">
-        <v>1192660.187378094</v>
+        <v>1219814.486476529</v>
       </c>
       <c r="Z19" t="n">
-        <v>69.31615173770209</v>
+        <v>69.39089863136371</v>
       </c>
     </row>
     <row r="20">
@@ -1841,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>25.26704545454545</v>
+        <v>25.26704545454546</v>
       </c>
       <c r="D20" t="n">
         <v>183.9318181818182</v>
@@ -1889,7 +1889,7 @@
         <v>69.91994422395237</v>
       </c>
       <c r="S20" t="n">
-        <v>2831504.159902598</v>
+        <v>2831504.159902597</v>
       </c>
       <c r="T20" t="n">
         <v>74.41547389305542</v>
@@ -1959,7 +1959,7 @@
         <v>70.38636363636363</v>
       </c>
       <c r="O21" t="n">
-        <v>25.13048875479437</v>
+        <v>25.13048875479438</v>
       </c>
       <c r="P21" t="n">
         <v>180.9187551847348</v>
@@ -2105,22 +2105,22 @@
         <v>75.71704545454546</v>
       </c>
       <c r="I23" t="n">
-        <v>26.05741626794259</v>
+        <v>26.07070707070707</v>
       </c>
       <c r="J23" t="n">
-        <v>182.6842105263158</v>
+        <v>182.7424242424243</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>70.47368421052632</v>
+        <v>70.45454545454544</v>
       </c>
       <c r="M23" t="n">
-        <v>2572368.421052631</v>
+        <v>2558207.07070707</v>
       </c>
       <c r="N23" t="n">
-        <v>74.23444976076556</v>
+        <v>74.2121212121212</v>
       </c>
       <c r="O23" t="n">
         <v>24.6143007556051</v>
@@ -2141,22 +2141,22 @@
         <v>73.64909265452744</v>
       </c>
       <c r="U23" t="n">
-        <v>25.21937256742749</v>
+        <v>25.2253870927784</v>
       </c>
       <c r="V23" t="n">
-        <v>182.5511065148937</v>
+        <v>182.4582667533754</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>68.28994341111044</v>
+        <v>68.2916480862133</v>
       </c>
       <c r="Y23" t="n">
-        <v>1967047.142195883</v>
+        <v>1968662.929931046</v>
       </c>
       <c r="Z23" t="n">
-        <v>73.30714222848091</v>
+        <v>73.34889704364342</v>
       </c>
     </row>
     <row r="24">
@@ -2515,22 +2515,22 @@
         <v>70.87700534759358</v>
       </c>
       <c r="I28" t="n">
-        <v>26.05741626794259</v>
+        <v>26.07070707070707</v>
       </c>
       <c r="J28" t="n">
-        <v>182.6842105263158</v>
+        <v>182.7424242424243</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>70.47368421052632</v>
+        <v>70.45454545454544</v>
       </c>
       <c r="M28" t="n">
-        <v>2572368.421052631</v>
+        <v>2558207.07070707</v>
       </c>
       <c r="N28" t="n">
-        <v>74.23444976076556</v>
+        <v>74.2121212121212</v>
       </c>
       <c r="O28" t="n">
         <v>23.96401371066244</v>
@@ -2551,22 +2551,22 @@
         <v>70.60957445485401</v>
       </c>
       <c r="U28" t="n">
-        <v>25.21937256742749</v>
+        <v>25.2253870927784</v>
       </c>
       <c r="V28" t="n">
-        <v>182.5511065148937</v>
+        <v>182.4582667533754</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>68.28994341111044</v>
+        <v>68.2916480862133</v>
       </c>
       <c r="Y28" t="n">
-        <v>1967047.142195883</v>
+        <v>1968662.929931046</v>
       </c>
       <c r="Z28" t="n">
-        <v>73.30714222848091</v>
+        <v>73.34889704364342</v>
       </c>
     </row>
     <row r="29">
@@ -2579,22 +2579,22 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>27.71139169472503</v>
+        <v>27.7473559120618</v>
       </c>
       <c r="D29" t="n">
-        <v>181.6445005611672</v>
+        <v>181.5882947118241</v>
       </c>
       <c r="E29" t="n">
-        <v>1.043434343434343</v>
+        <v>1.034224598930481</v>
       </c>
       <c r="F29" t="n">
-        <v>67.66812570145903</v>
+        <v>67.67801544860369</v>
       </c>
       <c r="G29" t="n">
-        <v>1479500</v>
+        <v>1467750</v>
       </c>
       <c r="H29" t="n">
-        <v>70.08355780022447</v>
+        <v>70.06494355317885</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -2603,22 +2603,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>25.51145559775422</v>
+        <v>25.55223640831731</v>
       </c>
       <c r="P29" t="n">
-        <v>178.8296919630501</v>
+        <v>178.8410642175611</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.039837852206273</v>
+        <v>1.036833661694343</v>
       </c>
       <c r="R29" t="n">
-        <v>65.12262567883849</v>
+        <v>65.21807424818194</v>
       </c>
       <c r="S29" t="n">
-        <v>1192660.187378094</v>
+        <v>1219814.486476529</v>
       </c>
       <c r="T29" t="n">
-        <v>69.31615173770209</v>
+        <v>69.39089863136371</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2940,7 +2940,7 @@
         <v>24.50582693175426</v>
       </c>
       <c r="V33" t="n">
-        <v>184.9363906840303</v>
+        <v>184.9363906840302</v>
       </c>
       <c r="W33" t="n">
         <v>1.145053993867822</v>

--- a/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -565,76 +565,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.29772727272727</v>
+        <v>25.96931818181818</v>
       </c>
       <c r="D2" t="n">
-        <v>184.0636363636364</v>
+        <v>184.3045454545455</v>
       </c>
       <c r="E2" t="n">
-        <v>1.192045454545455</v>
+        <v>1.198863636363636</v>
       </c>
       <c r="F2" t="n">
-        <v>73.4465909090909</v>
+        <v>72.93863636363636</v>
       </c>
       <c r="G2" t="n">
-        <v>6644872.159090909</v>
+        <v>6104289.772727272</v>
       </c>
       <c r="H2" t="n">
-        <v>77.7</v>
+        <v>77.51022727272726</v>
       </c>
       <c r="I2" t="n">
-        <v>27.99304812834225</v>
+        <v>27.89659090909091</v>
       </c>
       <c r="J2" t="n">
-        <v>182.7208556149733</v>
+        <v>183.0840909090909</v>
       </c>
       <c r="K2" t="n">
-        <v>2.428877005347593</v>
+        <v>2.380681818181818</v>
       </c>
       <c r="L2" t="n">
-        <v>82.85401069518717</v>
+        <v>82.68522727272727</v>
       </c>
       <c r="M2" t="n">
-        <v>40003743.31550803</v>
+        <v>38743181.81818181</v>
       </c>
       <c r="N2" t="n">
-        <v>84.67272727272727</v>
+        <v>84.55795454545455</v>
       </c>
       <c r="O2" t="n">
-        <v>26.65860588553603</v>
+        <v>26.42966036414566</v>
       </c>
       <c r="P2" t="n">
-        <v>184.5409919883357</v>
+        <v>184.9304761904762</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.39986415715276</v>
+        <v>1.330964635854342</v>
       </c>
       <c r="R2" t="n">
-        <v>70.64037415913336</v>
+        <v>69.99121323529413</v>
       </c>
       <c r="S2" t="n">
-        <v>3742602.524832534</v>
+        <v>3309505.558473389</v>
       </c>
       <c r="T2" t="n">
-        <v>74.10767259429025</v>
+        <v>73.83022584033614</v>
       </c>
       <c r="U2" t="n">
-        <v>27.105357461048</v>
+        <v>27.4938266886093</v>
       </c>
       <c r="V2" t="n">
-        <v>183.2180354186876</v>
+        <v>182.4515390145282</v>
       </c>
       <c r="W2" t="n">
-        <v>1.917764056536435</v>
+        <v>1.918102338482773</v>
       </c>
       <c r="X2" t="n">
-        <v>78.86880391891903</v>
+        <v>78.96189536108014</v>
       </c>
       <c r="Y2" t="n">
-        <v>24021291.4686313</v>
+        <v>23249631.7752296</v>
       </c>
       <c r="Z2" t="n">
-        <v>81.43710115166635</v>
+        <v>81.2590188193449</v>
       </c>
     </row>
     <row r="3">
@@ -647,76 +647,76 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>24.83522727272727</v>
+        <v>24.67012987012987</v>
       </c>
       <c r="D3" t="n">
-        <v>185.2846590909091</v>
+        <v>184.774025974026</v>
       </c>
       <c r="E3" t="n">
-        <v>1.048295454545455</v>
+        <v>1.068831168831169</v>
       </c>
       <c r="F3" t="n">
-        <v>70.28352272727273</v>
+        <v>69.61688311688312</v>
       </c>
       <c r="G3" t="n">
-        <v>3159488.636363637</v>
+        <v>2894285.714285714</v>
       </c>
       <c r="H3" t="n">
-        <v>75.71704545454546</v>
+        <v>75.32337662337662</v>
       </c>
       <c r="I3" t="n">
-        <v>26.38787878787879</v>
+        <v>26.23545454545455</v>
       </c>
       <c r="J3" t="n">
-        <v>183.3323232323232</v>
+        <v>183.5736363636364</v>
       </c>
       <c r="K3" t="n">
-        <v>1.674242424242424</v>
+        <v>1.617272727272727</v>
       </c>
       <c r="L3" t="n">
-        <v>76.55000000000001</v>
+        <v>76.33636363636364</v>
       </c>
       <c r="M3" t="n">
-        <v>12781414.14141414</v>
+        <v>12513090.90909091</v>
       </c>
       <c r="N3" t="n">
-        <v>79.64797979797979</v>
+        <v>79.51090909090908</v>
       </c>
       <c r="O3" t="n">
-        <v>24.6143007556051</v>
+        <v>25.21638707508273</v>
       </c>
       <c r="P3" t="n">
-        <v>184.460542665366</v>
+        <v>184.593419865159</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.093067748978075</v>
+        <v>1.106499177151351</v>
       </c>
       <c r="R3" t="n">
-        <v>68.31454288213799</v>
+        <v>68.52573171594911</v>
       </c>
       <c r="S3" t="n">
-        <v>2369897.367188468</v>
+        <v>2359444.897895985</v>
       </c>
       <c r="T3" t="n">
-        <v>73.64909265452744</v>
+        <v>73.46028870485392</v>
       </c>
       <c r="U3" t="n">
-        <v>25.21519608157313</v>
+        <v>25.26045917486922</v>
       </c>
       <c r="V3" t="n">
-        <v>181.6599116493724</v>
+        <v>181.9281685064062</v>
       </c>
       <c r="W3" t="n">
-        <v>1.546606690282089</v>
+        <v>1.571801725205773</v>
       </c>
       <c r="X3" t="n">
-        <v>74.63072168035612</v>
+        <v>74.77021995992236</v>
       </c>
       <c r="Y3" t="n">
-        <v>11503672.51446466</v>
+        <v>11508767.54879581</v>
       </c>
       <c r="Z3" t="n">
-        <v>79.02916922635656</v>
+        <v>79.13635406991254</v>
       </c>
     </row>
     <row r="4">
@@ -729,76 +729,76 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>25.47935606060606</v>
+        <v>25.32007575757576</v>
       </c>
       <c r="D4" t="n">
-        <v>184.7681186868687</v>
+        <v>184.4032828282828</v>
       </c>
       <c r="E4" t="n">
-        <v>1.867234848484848</v>
+        <v>1.785606060606061</v>
       </c>
       <c r="F4" t="n">
-        <v>80.88080808080809</v>
+        <v>80.18093434343434</v>
       </c>
       <c r="G4" t="n">
-        <v>36151303.66161616</v>
+        <v>32740675.50505051</v>
       </c>
       <c r="H4" t="n">
-        <v>84.36047979797981</v>
+        <v>83.91527777777777</v>
       </c>
       <c r="I4" t="n">
-        <v>25.89946524064171</v>
+        <v>25.84431818181818</v>
       </c>
       <c r="J4" t="n">
-        <v>186.2572192513369</v>
+        <v>186.2375</v>
       </c>
       <c r="K4" t="n">
-        <v>1.275935828877006</v>
+        <v>1.235227272727273</v>
       </c>
       <c r="L4" t="n">
-        <v>75.78983957219252</v>
+        <v>76.16022727272727</v>
       </c>
       <c r="M4" t="n">
-        <v>12650855.61497326</v>
+        <v>13589204.54545454</v>
       </c>
       <c r="N4" t="n">
-        <v>79.04010695187166</v>
+        <v>79.38636363636363</v>
       </c>
       <c r="O4" t="n">
-        <v>24.48059814682097</v>
+        <v>24.41531288156288</v>
       </c>
       <c r="P4" t="n">
-        <v>184.004159411442</v>
+        <v>184.9628663003663</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.532936098724142</v>
+        <v>1.539888583638584</v>
       </c>
       <c r="R4" t="n">
-        <v>76.37470707030489</v>
+        <v>76.22067562067562</v>
       </c>
       <c r="S4" t="n">
-        <v>20609008.02222133</v>
+        <v>21966995.34493284</v>
       </c>
       <c r="T4" t="n">
-        <v>82.22238245651289</v>
+        <v>82.03118030118029</v>
       </c>
       <c r="U4" t="n">
-        <v>24.57152140523933</v>
+        <v>25.07500434882884</v>
       </c>
       <c r="V4" t="n">
-        <v>185.391205899366</v>
+        <v>184.7674292753385</v>
       </c>
       <c r="W4" t="n">
-        <v>1.16637106491948</v>
+        <v>1.219184687431591</v>
       </c>
       <c r="X4" t="n">
-        <v>72.04009418022972</v>
+        <v>72.01683930051286</v>
       </c>
       <c r="Y4" t="n">
-        <v>6506192.078869222</v>
+        <v>5636406.245113675</v>
       </c>
       <c r="Z4" t="n">
-        <v>76.63134153362353</v>
+        <v>75.79466071316884</v>
       </c>
     </row>
     <row r="5">
@@ -811,76 +811,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25.26704545454546</v>
+        <v>25.53409090909091</v>
       </c>
       <c r="D5" t="n">
-        <v>183.9318181818182</v>
+        <v>183.9772727272727</v>
       </c>
       <c r="E5" t="n">
-        <v>1.039772727272727</v>
+        <v>1.034090909090909</v>
       </c>
       <c r="F5" t="n">
-        <v>72.38068181818181</v>
+        <v>72.38636363636364</v>
       </c>
       <c r="G5" t="n">
-        <v>4611931.818181818</v>
+        <v>4504545.454545455</v>
       </c>
       <c r="H5" t="n">
-        <v>76.28977272727273</v>
+        <v>76.01136363636363</v>
       </c>
       <c r="I5" t="n">
-        <v>25.43011363636364</v>
+        <v>25.52840909090909</v>
       </c>
       <c r="J5" t="n">
-        <v>183.9176136363636</v>
+        <v>183.5920454545455</v>
       </c>
       <c r="K5" t="n">
-        <v>1.35625</v>
+        <v>1.353409090909091</v>
       </c>
       <c r="L5" t="n">
-        <v>73.73693181818182</v>
+        <v>73.40568181818182</v>
       </c>
       <c r="M5" t="n">
-        <v>7957500</v>
+        <v>7352272.727272728</v>
       </c>
       <c r="N5" t="n">
-        <v>78.09261363636364</v>
+        <v>77.5443181818182</v>
       </c>
       <c r="O5" t="n">
-        <v>25.25982563380661</v>
+        <v>24.95436507936508</v>
       </c>
       <c r="P5" t="n">
-        <v>182.8208103038266</v>
+        <v>182.1184752747253</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.161642315514598</v>
+        <v>1.133648758648758</v>
       </c>
       <c r="R5" t="n">
-        <v>69.91994422395237</v>
+        <v>69.99778693528694</v>
       </c>
       <c r="S5" t="n">
-        <v>2831504.159902597</v>
+        <v>3049588.039275539</v>
       </c>
       <c r="T5" t="n">
-        <v>74.41547389305542</v>
+        <v>74.91550925925927</v>
       </c>
       <c r="U5" t="n">
-        <v>25.25337394813735</v>
+        <v>25.58548541434411</v>
       </c>
       <c r="V5" t="n">
-        <v>182.7666355829259</v>
+        <v>182.2128460609439</v>
       </c>
       <c r="W5" t="n">
-        <v>1.238638795109466</v>
+        <v>1.291151523597176</v>
       </c>
       <c r="X5" t="n">
-        <v>71.17697368444136</v>
+        <v>71.43976673789174</v>
       </c>
       <c r="Y5" t="n">
-        <v>4022459.930200689</v>
+        <v>4134585.859113712</v>
       </c>
       <c r="Z5" t="n">
-        <v>76.73910066181804</v>
+        <v>76.88763610182087</v>
       </c>
     </row>
     <row r="6">
@@ -893,76 +893,76 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>24.50267379679144</v>
+        <v>24.53409090909091</v>
       </c>
       <c r="D6" t="n">
-        <v>185.3529411764706</v>
+        <v>185.4318181818182</v>
       </c>
       <c r="E6" t="n">
-        <v>1.283422459893048</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="F6" t="n">
-        <v>75.51336898395722</v>
+        <v>75.04545454545455</v>
       </c>
       <c r="G6" t="n">
-        <v>12267647.05882353</v>
+        <v>11312500</v>
       </c>
       <c r="H6" t="n">
-        <v>80.08556149732621</v>
+        <v>79.71590909090909</v>
       </c>
       <c r="I6" t="n">
-        <v>25.01704545454545</v>
+        <v>24.76136363636364</v>
       </c>
       <c r="J6" t="n">
-        <v>186.5568181818182</v>
+        <v>187.1022727272727</v>
       </c>
       <c r="K6" t="n">
         <v>1.045454545454545</v>
       </c>
       <c r="L6" t="n">
-        <v>73.23863636363636</v>
+        <v>73.22727272727272</v>
       </c>
       <c r="M6" t="n">
-        <v>5014772.727272727</v>
+        <v>5114772.727272728</v>
       </c>
       <c r="N6" t="n">
-        <v>77.01136363636363</v>
+        <v>77.31818181818181</v>
       </c>
       <c r="O6" t="n">
-        <v>23.31207926023342</v>
+        <v>22.95725779967159</v>
       </c>
       <c r="P6" t="n">
-        <v>184.9216622994615</v>
+        <v>184.7881506568145</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.195436060070948</v>
+        <v>1.199683908045977</v>
       </c>
       <c r="R6" t="n">
-        <v>71.49482277320006</v>
+        <v>71.18593185550083</v>
       </c>
       <c r="S6" t="n">
-        <v>7080806.646118512</v>
+        <v>6894173.850574713</v>
       </c>
       <c r="T6" t="n">
-        <v>77.97766870909872</v>
+        <v>78.07766420361247</v>
       </c>
       <c r="U6" t="n">
-        <v>25.37884961035697</v>
+        <v>25.23056374045344</v>
       </c>
       <c r="V6" t="n">
-        <v>183.0324518931504</v>
+        <v>182.9242851456822</v>
       </c>
       <c r="W6" t="n">
-        <v>1.068791702578467</v>
+        <v>1.07821222078575</v>
       </c>
       <c r="X6" t="n">
-        <v>71.0619448484522</v>
+        <v>70.69103840467811</v>
       </c>
       <c r="Y6" t="n">
-        <v>3350950.734620771</v>
+        <v>3164777.944618018</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.96703823409706</v>
+        <v>74.7301565455242</v>
       </c>
     </row>
     <row r="7">
@@ -975,76 +975,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.08522727272727</v>
+        <v>24.97727272727273</v>
       </c>
       <c r="D7" t="n">
-        <v>184.1647727272727</v>
+        <v>183.9772727272727</v>
       </c>
       <c r="E7" t="n">
-        <v>1.147727272727273</v>
+        <v>1.125</v>
       </c>
       <c r="F7" t="n">
-        <v>73.20454545454545</v>
+        <v>72.88636363636363</v>
       </c>
       <c r="G7" t="n">
-        <v>4914062.5</v>
+        <v>4686079.545454545</v>
       </c>
       <c r="H7" t="n">
-        <v>76.71590909090909</v>
+        <v>76.55681818181819</v>
       </c>
       <c r="I7" t="n">
-        <v>26.40588235294118</v>
+        <v>26.18636363636364</v>
       </c>
       <c r="J7" t="n">
-        <v>181.8941176470588</v>
+        <v>182.5409090909091</v>
       </c>
       <c r="K7" t="n">
-        <v>1.721925133689839</v>
+        <v>1.7125</v>
       </c>
       <c r="L7" t="n">
-        <v>80.77593582887701</v>
+        <v>80.72272727272728</v>
       </c>
       <c r="M7" t="n">
-        <v>35282459.89304812</v>
+        <v>35875681.81818182</v>
       </c>
       <c r="N7" t="n">
-        <v>82.47647058823529</v>
+        <v>82.60454545454546</v>
       </c>
       <c r="O7" t="n">
-        <v>24.14795037138787</v>
+        <v>24.08346688034188</v>
       </c>
       <c r="P7" t="n">
-        <v>182.896041921042</v>
+        <v>182.8111645299145</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.031994047619047</v>
+        <v>1.045800264550265</v>
       </c>
       <c r="R7" t="n">
-        <v>70.53455051892551</v>
+        <v>70.58381664631665</v>
       </c>
       <c r="S7" t="n">
-        <v>3296554.264601139</v>
+        <v>3419376.717032967</v>
       </c>
       <c r="T7" t="n">
-        <v>75.27486581705331</v>
+        <v>75.36137184574685</v>
       </c>
       <c r="U7" t="n">
-        <v>25.13048875479438</v>
+        <v>24.8723784868812</v>
       </c>
       <c r="V7" t="n">
-        <v>180.9187551847348</v>
+        <v>180.7384918913073</v>
       </c>
       <c r="W7" t="n">
-        <v>1.588658208500044</v>
+        <v>1.526548378522063</v>
       </c>
       <c r="X7" t="n">
-        <v>76.11886165408519</v>
+        <v>75.77367782572891</v>
       </c>
       <c r="Y7" t="n">
-        <v>15461897.2773681</v>
+        <v>16078138.33966601</v>
       </c>
       <c r="Z7" t="n">
-        <v>79.30405093073888</v>
+        <v>79.16112704052912</v>
       </c>
     </row>
     <row r="8">
@@ -1057,76 +1057,76 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>25.71590909090909</v>
+        <v>25.15909090909091</v>
       </c>
       <c r="D8" t="n">
-        <v>184.4261363636363</v>
+        <v>184.2159090909091</v>
       </c>
       <c r="E8" t="n">
-        <v>1.255681818181818</v>
+        <v>1.193181818181818</v>
       </c>
       <c r="F8" t="n">
-        <v>72.30681818181819</v>
+        <v>72.13636363636363</v>
       </c>
       <c r="G8" t="n">
-        <v>3672159.090909091</v>
+        <v>3732954.545454545</v>
       </c>
       <c r="H8" t="n">
-        <v>75.59090909090909</v>
+        <v>76.04545454545455</v>
       </c>
       <c r="I8" t="n">
-        <v>26.80454545454545</v>
+        <v>26.32727272727273</v>
       </c>
       <c r="J8" t="n">
-        <v>183.00625</v>
+        <v>182.5181818181819</v>
       </c>
       <c r="K8" t="n">
-        <v>2.241477272727272</v>
+        <v>2.140909090909091</v>
       </c>
       <c r="L8" t="n">
-        <v>79.00965909090908</v>
+        <v>78.7090909090909</v>
       </c>
       <c r="M8" t="n">
-        <v>22312159.09090909</v>
+        <v>21836590.90909091</v>
       </c>
       <c r="N8" t="n">
-        <v>80.66079545454545</v>
+        <v>80.61931818181819</v>
       </c>
       <c r="O8" t="n">
-        <v>26.06799560193957</v>
+        <v>26.04532414424656</v>
       </c>
       <c r="P8" t="n">
-        <v>183.2890014718679</v>
+        <v>183.1759994316029</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.172249238628549</v>
+        <v>1.157476790450929</v>
       </c>
       <c r="R8" t="n">
-        <v>70.40985590080419</v>
+        <v>70.18014320449666</v>
       </c>
       <c r="S8" t="n">
-        <v>2738662.492061738</v>
+        <v>2674243.747631679</v>
       </c>
       <c r="T8" t="n">
-        <v>74.30863840820737</v>
+        <v>74.09126799924215</v>
       </c>
       <c r="U8" t="n">
-        <v>25.1649596771364</v>
+        <v>25.44432462492808</v>
       </c>
       <c r="V8" t="n">
-        <v>182.5540512110016</v>
+        <v>183.1988411452851</v>
       </c>
       <c r="W8" t="n">
-        <v>1.93875424543528</v>
+        <v>1.967550752249028</v>
       </c>
       <c r="X8" t="n">
-        <v>76.14382067684869</v>
+        <v>76.30858608584902</v>
       </c>
       <c r="Y8" t="n">
-        <v>16244290.40049191</v>
+        <v>16928452.01693262</v>
       </c>
       <c r="Z8" t="n">
-        <v>80.56642726885184</v>
+        <v>80.43082664063267</v>
       </c>
     </row>
     <row r="9">
@@ -1139,76 +1139,76 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>27.00983519404572</v>
+        <v>26.72323232323232</v>
       </c>
       <c r="D9" t="n">
-        <v>183.748591174907</v>
+        <v>183.9272727272727</v>
       </c>
       <c r="E9" t="n">
-        <v>1.771451355661882</v>
+        <v>1.732323232323232</v>
       </c>
       <c r="F9" t="n">
-        <v>77.9136629452419</v>
+        <v>77.44242424242424</v>
       </c>
       <c r="G9" t="n">
-        <v>18644630.51568315</v>
+        <v>17936565.65656566</v>
       </c>
       <c r="H9" t="n">
-        <v>80.03056884635834</v>
+        <v>79.7929292929293</v>
       </c>
       <c r="I9" t="n">
-        <v>24.90909090909091</v>
+        <v>24.86776859504132</v>
       </c>
       <c r="J9" t="n">
-        <v>184.6772727272727</v>
+        <v>184.801652892562</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>70.05</v>
+        <v>69.91735537190083</v>
       </c>
       <c r="M9" t="n">
-        <v>2789659.090909091</v>
+        <v>2747314.049586777</v>
       </c>
       <c r="N9" t="n">
-        <v>74.65909090909091</v>
+        <v>74.55371900826447</v>
       </c>
       <c r="O9" t="n">
-        <v>26.30585867623083</v>
+        <v>26.36574225418619</v>
       </c>
       <c r="P9" t="n">
-        <v>182.0373385877842</v>
+        <v>182.0992498263666</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.804168915110743</v>
+        <v>1.769734558178494</v>
       </c>
       <c r="R9" t="n">
-        <v>76.34267373933758</v>
+        <v>76.45813842907666</v>
       </c>
       <c r="S9" t="n">
-        <v>15912681.51152446</v>
+        <v>15930104.30886175</v>
       </c>
       <c r="T9" t="n">
-        <v>79.57422905088809</v>
+        <v>79.51491332635497</v>
       </c>
       <c r="U9" t="n">
-        <v>25.88763636363636</v>
+        <v>25.70307692307692</v>
       </c>
       <c r="V9" t="n">
-        <v>181.2584195804196</v>
+        <v>181.7978385251113</v>
       </c>
       <c r="W9" t="n">
-        <v>1.041741258741259</v>
+        <v>1.036020343293071</v>
       </c>
       <c r="X9" t="n">
-        <v>67.43983216783218</v>
+        <v>67.48634456452638</v>
       </c>
       <c r="Y9" t="n">
-        <v>1614444.055944056</v>
+        <v>1625925.047679593</v>
       </c>
       <c r="Z9" t="n">
-        <v>72.04871328671328</v>
+        <v>72.29641449459632</v>
       </c>
     </row>
     <row r="10">
@@ -1221,76 +1221,76 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>24.22424242424243</v>
+        <v>23.98863636363636</v>
       </c>
       <c r="D10" t="n">
-        <v>184.2242424242424</v>
+        <v>184.5227272727273</v>
       </c>
       <c r="E10" t="n">
-        <v>1.006060606060606</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>72.31515151515153</v>
+        <v>72</v>
       </c>
       <c r="G10" t="n">
-        <v>5439696.96969697</v>
+        <v>5391477.272727273</v>
       </c>
       <c r="H10" t="n">
-        <v>77.56363636363636</v>
+        <v>77.80681818181819</v>
       </c>
       <c r="I10" t="n">
-        <v>25.72</v>
+        <v>25.75537190082645</v>
       </c>
       <c r="J10" t="n">
-        <v>187.4404545454545</v>
+        <v>187.2752066115702</v>
       </c>
       <c r="K10" t="n">
-        <v>1.515454545454545</v>
+        <v>1.52396694214876</v>
       </c>
       <c r="L10" t="n">
-        <v>78.34818181818181</v>
+        <v>78.25785123966942</v>
       </c>
       <c r="M10" t="n">
-        <v>19184318.18181818</v>
+        <v>19109917.3553719</v>
       </c>
       <c r="N10" t="n">
-        <v>81.74727272727273</v>
+        <v>81.68429752066116</v>
       </c>
       <c r="O10" t="n">
-        <v>23.3850240194588</v>
+        <v>23.22237078139252</v>
       </c>
       <c r="P10" t="n">
-        <v>182.5975408938887</v>
+        <v>183.2658117968988</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.088268774703557</v>
+        <v>1.069461842505321</v>
       </c>
       <c r="R10" t="n">
-        <v>68.49635471774603</v>
+        <v>68.05325554879903</v>
       </c>
       <c r="S10" t="n">
-        <v>2727761.91344887</v>
+        <v>2579401.92687747</v>
       </c>
       <c r="T10" t="n">
-        <v>75.08297638593291</v>
+        <v>74.7467338096686</v>
       </c>
       <c r="U10" t="n">
-        <v>25.61432364495408</v>
+        <v>25.38361215493627</v>
       </c>
       <c r="V10" t="n">
-        <v>186.6529753909537</v>
+        <v>186.6604602760729</v>
       </c>
       <c r="W10" t="n">
-        <v>1.416610934958761</v>
+        <v>1.364253017513887</v>
       </c>
       <c r="X10" t="n">
-        <v>75.16742954469041</v>
+        <v>74.84356183488593</v>
       </c>
       <c r="Y10" t="n">
-        <v>13296373.77320546</v>
+        <v>13401761.69949945</v>
       </c>
       <c r="Z10" t="n">
-        <v>78.97318542648978</v>
+        <v>78.7814826112257</v>
       </c>
     </row>
     <row r="11">
@@ -1303,76 +1303,76 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>25.80065124933546</v>
+        <v>25.70012626262626</v>
       </c>
       <c r="D11" t="n">
-        <v>186.4420919723551</v>
+        <v>186.4155303030303</v>
       </c>
       <c r="E11" t="n">
-        <v>1.809688995215311</v>
+        <v>1.789520202020202</v>
       </c>
       <c r="F11" t="n">
-        <v>80.37547846889952</v>
+        <v>80.31452020202019</v>
       </c>
       <c r="G11" t="n">
-        <v>29706951.08984582</v>
+        <v>30109873.73737373</v>
       </c>
       <c r="H11" t="n">
-        <v>83.93491493886232</v>
+        <v>83.91856060606059</v>
       </c>
       <c r="I11" t="n">
-        <v>26.09488636363636</v>
+        <v>25.81904761904762</v>
       </c>
       <c r="J11" t="n">
-        <v>182.0313131313131</v>
+        <v>181.2777777777778</v>
       </c>
       <c r="K11" t="n">
-        <v>1.092550505050505</v>
+        <v>1.044444444444445</v>
       </c>
       <c r="L11" t="n">
-        <v>71.28573232323234</v>
+        <v>71.04126984126985</v>
       </c>
       <c r="M11" t="n">
-        <v>3390509.785353535</v>
+        <v>3379007.936507937</v>
       </c>
       <c r="N11" t="n">
-        <v>73.5072601010101</v>
+        <v>73.44603174603175</v>
       </c>
       <c r="O11" t="n">
-        <v>24.59595455510005</v>
+        <v>24.95681017266487</v>
       </c>
       <c r="P11" t="n">
-        <v>183.7342937296087</v>
+        <v>183.9841642974366</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.732917092676216</v>
+        <v>1.787877817072325</v>
       </c>
       <c r="R11" t="n">
-        <v>75.57961849791249</v>
+        <v>76.4989776367797</v>
       </c>
       <c r="S11" t="n">
-        <v>14379449.33362635</v>
+        <v>16456180.72429097</v>
       </c>
       <c r="T11" t="n">
-        <v>81.34020879377557</v>
+        <v>81.71066422809329</v>
       </c>
       <c r="U11" t="n">
-        <v>25.53798662278921</v>
+        <v>26.30193732193732</v>
       </c>
       <c r="V11" t="n">
-        <v>182.9264350690574</v>
+        <v>183.4291900691901</v>
       </c>
       <c r="W11" t="n">
-        <v>1.187009844257287</v>
+        <v>1.247944647944648</v>
       </c>
       <c r="X11" t="n">
-        <v>68.93913274660477</v>
+        <v>69.90273504273503</v>
       </c>
       <c r="Y11" t="n">
-        <v>2350843.943674878</v>
+        <v>2647104.029304029</v>
       </c>
       <c r="Z11" t="n">
-        <v>72.42308060436177</v>
+        <v>72.62474562474563</v>
       </c>
     </row>
     <row r="12">
@@ -1442,7 +1442,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1513,76 +1513,76 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>25.55026737967914</v>
+        <v>25.74204545454545</v>
       </c>
       <c r="D16" t="n">
-        <v>186.6604278074867</v>
+        <v>186.9363636363636</v>
       </c>
       <c r="E16" t="n">
-        <v>1.187700534759358</v>
+        <v>1.214772727272727</v>
       </c>
       <c r="F16" t="n">
-        <v>73.5529411764706</v>
+        <v>73.25</v>
       </c>
       <c r="G16" t="n">
-        <v>5926871.657754011</v>
+        <v>5306079.545454546</v>
       </c>
       <c r="H16" t="n">
-        <v>77.51925133689839</v>
+        <v>77.25454545454545</v>
       </c>
       <c r="I16" t="n">
-        <v>26.12897727272728</v>
+        <v>25.44285714285714</v>
       </c>
       <c r="J16" t="n">
-        <v>184.0391414141414</v>
+        <v>183.563492063492</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>66.85138888888889</v>
+        <v>66.64603174603175</v>
       </c>
       <c r="M16" t="n">
-        <v>1185452.967171717</v>
+        <v>1211587.301587302</v>
       </c>
       <c r="N16" t="n">
-        <v>69.99785353535353</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="O16" t="n">
-        <v>24.50582693175426</v>
+        <v>24.18748135890846</v>
       </c>
       <c r="P16" t="n">
-        <v>184.9363906840302</v>
+        <v>185.0565917079616</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.145053993867822</v>
+        <v>1.13142152900961</v>
       </c>
       <c r="R16" t="n">
-        <v>71.03316229230067</v>
+        <v>70.81202993245441</v>
       </c>
       <c r="S16" t="n">
-        <v>4184631.048136781</v>
+        <v>3964935.51087704</v>
       </c>
       <c r="T16" t="n">
-        <v>77.17398527429526</v>
+        <v>77.16509865602913</v>
       </c>
       <c r="U16" t="n">
-        <v>24.87265791575574</v>
+        <v>24.89280560709132</v>
       </c>
       <c r="V16" t="n">
-        <v>183.4896629849619</v>
+        <v>183.361605854463</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>64.88296396990691</v>
+        <v>64.58005875077303</v>
       </c>
       <c r="Y16" t="n">
-        <v>1058988.863883701</v>
+        <v>1031453.133374562</v>
       </c>
       <c r="Z16" t="n">
-        <v>69.34134413593652</v>
+        <v>69.26774582560297</v>
       </c>
     </row>
     <row r="17">
@@ -1595,76 +1595,76 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>26.29772727272727</v>
+        <v>25.96931818181818</v>
       </c>
       <c r="D17" t="n">
-        <v>184.0636363636364</v>
+        <v>184.3045454545455</v>
       </c>
       <c r="E17" t="n">
-        <v>1.192045454545455</v>
+        <v>1.198863636363636</v>
       </c>
       <c r="F17" t="n">
-        <v>73.4465909090909</v>
+        <v>72.93863636363636</v>
       </c>
       <c r="G17" t="n">
-        <v>6644872.159090909</v>
+        <v>6104289.772727272</v>
       </c>
       <c r="H17" t="n">
-        <v>77.7</v>
+        <v>77.51022727272726</v>
       </c>
       <c r="I17" t="n">
-        <v>26.04772727272727</v>
+        <v>26.08051948051948</v>
       </c>
       <c r="J17" t="n">
-        <v>184.8403409090909</v>
+        <v>184.2207792207792</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>65.97727272727273</v>
+        <v>65.64805194805194</v>
       </c>
       <c r="M17" t="n">
-        <v>1178267.045454545</v>
+        <v>1164110.389610389</v>
       </c>
       <c r="N17" t="n">
-        <v>69.29375</v>
+        <v>68.99999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>26.65860588553603</v>
+        <v>26.42966036414566</v>
       </c>
       <c r="P17" t="n">
-        <v>184.5409919883357</v>
+        <v>184.9304761904762</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.39986415715276</v>
+        <v>1.330964635854342</v>
       </c>
       <c r="R17" t="n">
-        <v>70.64037415913336</v>
+        <v>69.99121323529413</v>
       </c>
       <c r="S17" t="n">
-        <v>3742602.524832534</v>
+        <v>3309505.558473389</v>
       </c>
       <c r="T17" t="n">
-        <v>74.10767259429025</v>
+        <v>73.83022584033614</v>
       </c>
       <c r="U17" t="n">
-        <v>26.03236695621207</v>
+        <v>26.15596963423051</v>
       </c>
       <c r="V17" t="n">
-        <v>182.606010776663</v>
+        <v>182.3768115942029</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>64.42874415489905</v>
+        <v>64.2716816195077</v>
       </c>
       <c r="Y17" t="n">
-        <v>1062892.325305029</v>
+        <v>1000485.480702872</v>
       </c>
       <c r="Z17" t="n">
-        <v>68.1845579013378</v>
+        <v>67.93227867140909</v>
       </c>
     </row>
     <row r="18">
@@ -1677,76 +1677,76 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25.43011363636364</v>
+        <v>25.52840909090909</v>
       </c>
       <c r="D18" t="n">
-        <v>183.9176136363636</v>
+        <v>183.5920454545455</v>
       </c>
       <c r="E18" t="n">
-        <v>1.35625</v>
+        <v>1.353409090909091</v>
       </c>
       <c r="F18" t="n">
-        <v>73.73693181818182</v>
+        <v>73.40568181818182</v>
       </c>
       <c r="G18" t="n">
-        <v>7957500</v>
+        <v>7352272.727272728</v>
       </c>
       <c r="H18" t="n">
-        <v>78.09261363636364</v>
+        <v>77.5443181818182</v>
       </c>
       <c r="I18" t="n">
-        <v>28.85</v>
+        <v>28.87142857142857</v>
       </c>
       <c r="J18" t="n">
-        <v>183.7528409090909</v>
+        <v>183.4142857142857</v>
       </c>
       <c r="K18" t="n">
-        <v>1.147727272727273</v>
+        <v>1.157142857142857</v>
       </c>
       <c r="L18" t="n">
-        <v>67.9153409090909</v>
+        <v>67.78571428571429</v>
       </c>
       <c r="M18" t="n">
-        <v>1070465.909090909</v>
+        <v>1045500</v>
       </c>
       <c r="N18" t="n">
-        <v>70.03011363636364</v>
+        <v>69.98571428571428</v>
       </c>
       <c r="O18" t="n">
-        <v>25.25337394813735</v>
+        <v>25.58548541434411</v>
       </c>
       <c r="P18" t="n">
-        <v>182.7666355829259</v>
+        <v>182.2128460609439</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.238638795109466</v>
+        <v>1.291151523597176</v>
       </c>
       <c r="R18" t="n">
-        <v>71.17697368444136</v>
+        <v>71.43976673789174</v>
       </c>
       <c r="S18" t="n">
-        <v>4022459.930200689</v>
+        <v>4134585.859113712</v>
       </c>
       <c r="T18" t="n">
-        <v>76.73910066181804</v>
+        <v>76.88763610182087</v>
       </c>
       <c r="U18" t="n">
-        <v>25.20870246299594</v>
+        <v>25.22084760994699</v>
       </c>
       <c r="V18" t="n">
-        <v>184.9972915610959</v>
+        <v>185.1004652191609</v>
       </c>
       <c r="W18" t="n">
-        <v>1.045622275771732</v>
+        <v>1.035889359088117</v>
       </c>
       <c r="X18" t="n">
-        <v>65.18824455536412</v>
+        <v>65.26384562297606</v>
       </c>
       <c r="Y18" t="n">
-        <v>987446.7169027631</v>
+        <v>999487.5229727715</v>
       </c>
       <c r="Z18" t="n">
-        <v>68.72725022964153</v>
+        <v>68.73200984890426</v>
       </c>
     </row>
     <row r="19">
@@ -1759,76 +1759,76 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>26.82929292929293</v>
+        <v>26.78567493112947</v>
       </c>
       <c r="D19" t="n">
-        <v>185.6604545454546</v>
+        <v>185.6598714416896</v>
       </c>
       <c r="E19" t="n">
-        <v>1.075909090909091</v>
+        <v>1.085123966942149</v>
       </c>
       <c r="F19" t="n">
-        <v>69.71712121212121</v>
+        <v>69.30918273645547</v>
       </c>
       <c r="G19" t="n">
-        <v>2019979.797979798</v>
+        <v>1959320.477502296</v>
       </c>
       <c r="H19" t="n">
-        <v>73.00373737373738</v>
+        <v>72.65656565656565</v>
       </c>
       <c r="I19" t="n">
-        <v>27.7473559120618</v>
+        <v>27.89450056116723</v>
       </c>
       <c r="J19" t="n">
-        <v>181.5882947118241</v>
+        <v>180.9455667789001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.034224598930481</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>67.67801544860369</v>
+        <v>67.60897867564535</v>
       </c>
       <c r="M19" t="n">
-        <v>1467750</v>
+        <v>1260000</v>
       </c>
       <c r="N19" t="n">
-        <v>70.06494355317885</v>
+        <v>69.80953984287318</v>
       </c>
       <c r="O19" t="n">
-        <v>26.98757034632035</v>
+        <v>27.35946734424995</v>
       </c>
       <c r="P19" t="n">
-        <v>185.3590241624318</v>
+        <v>185.3063988843831</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.133275574063617</v>
+        <v>1.12314477354003</v>
       </c>
       <c r="R19" t="n">
-        <v>69.62046988518728</v>
+        <v>70.03460688191913</v>
       </c>
       <c r="S19" t="n">
-        <v>2075383.015716168</v>
+        <v>2126572.170747566</v>
       </c>
       <c r="T19" t="n">
-        <v>73.06944939299831</v>
+        <v>73.13433396642883</v>
       </c>
       <c r="U19" t="n">
-        <v>25.55223640831731</v>
+        <v>25.19443532313097</v>
       </c>
       <c r="V19" t="n">
-        <v>178.8410642175611</v>
+        <v>178.4018239248674</v>
       </c>
       <c r="W19" t="n">
-        <v>1.036833661694343</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>65.21807424818194</v>
+        <v>65.03192696192696</v>
       </c>
       <c r="Y19" t="n">
-        <v>1219814.486476529</v>
+        <v>1260961.610129001</v>
       </c>
       <c r="Z19" t="n">
-        <v>69.39089863136371</v>
+        <v>69.59661227661228</v>
       </c>
     </row>
     <row r="20">
@@ -1841,76 +1841,76 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>25.26704545454546</v>
+        <v>25.53409090909091</v>
       </c>
       <c r="D20" t="n">
-        <v>183.9318181818182</v>
+        <v>183.9772727272727</v>
       </c>
       <c r="E20" t="n">
-        <v>1.039772727272727</v>
+        <v>1.034090909090909</v>
       </c>
       <c r="F20" t="n">
-        <v>72.38068181818181</v>
+        <v>72.38636363636364</v>
       </c>
       <c r="G20" t="n">
-        <v>4611931.818181818</v>
+        <v>4504545.454545455</v>
       </c>
       <c r="H20" t="n">
-        <v>76.28977272727273</v>
+        <v>76.01136363636363</v>
       </c>
       <c r="I20" t="n">
-        <v>26.84976076555024</v>
+        <v>26.86</v>
       </c>
       <c r="J20" t="n">
-        <v>181.4129186602871</v>
+        <v>181.6572727272727</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>67.53779904306221</v>
+        <v>67.4309090909091</v>
       </c>
       <c r="M20" t="n">
-        <v>1317033.492822966</v>
+        <v>1277590.909090909</v>
       </c>
       <c r="N20" t="n">
-        <v>70.63827751196173</v>
+        <v>70.28545454545454</v>
       </c>
       <c r="O20" t="n">
-        <v>25.25982563380661</v>
+        <v>24.95436507936508</v>
       </c>
       <c r="P20" t="n">
-        <v>182.8208103038266</v>
+        <v>182.1184752747253</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.161642315514598</v>
+        <v>1.133648758648758</v>
       </c>
       <c r="R20" t="n">
-        <v>69.91994422395237</v>
+        <v>69.99778693528694</v>
       </c>
       <c r="S20" t="n">
-        <v>2831504.159902597</v>
+        <v>3049588.039275539</v>
       </c>
       <c r="T20" t="n">
-        <v>74.41547389305542</v>
+        <v>74.91550925925927</v>
       </c>
       <c r="U20" t="n">
-        <v>25.28923867216773</v>
+        <v>25.63088518888519</v>
       </c>
       <c r="V20" t="n">
-        <v>179.4360243633813</v>
+        <v>179.4868835053835</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>66.08823967540215</v>
+        <v>66.03421056721056</v>
       </c>
       <c r="Y20" t="n">
-        <v>1242947.921008562</v>
+        <v>1188850.593850594</v>
       </c>
       <c r="Z20" t="n">
-        <v>71.20271346671805</v>
+        <v>70.69366881266882</v>
       </c>
     </row>
     <row r="21">
@@ -1923,76 +1923,76 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>26.40588235294118</v>
+        <v>26.18636363636364</v>
       </c>
       <c r="D21" t="n">
-        <v>181.8941176470588</v>
+        <v>182.5409090909091</v>
       </c>
       <c r="E21" t="n">
-        <v>1.721925133689839</v>
+        <v>1.7125</v>
       </c>
       <c r="F21" t="n">
-        <v>80.77593582887701</v>
+        <v>80.72272727272728</v>
       </c>
       <c r="G21" t="n">
-        <v>35282459.89304812</v>
+        <v>35875681.81818182</v>
       </c>
       <c r="H21" t="n">
-        <v>82.47647058823529</v>
+        <v>82.60454545454546</v>
       </c>
       <c r="I21" t="n">
-        <v>25.72727272727273</v>
+        <v>26.41558441558441</v>
       </c>
       <c r="J21" t="n">
-        <v>184.2102272727273</v>
+        <v>184.3896103896104</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>66.59090909090909</v>
+        <v>67.1948051948052</v>
       </c>
       <c r="M21" t="n">
-        <v>1288068.181818182</v>
+        <v>1326623.376623377</v>
       </c>
       <c r="N21" t="n">
-        <v>70.38636363636363</v>
+        <v>70.55844155844156</v>
       </c>
       <c r="O21" t="n">
-        <v>25.13048875479438</v>
+        <v>24.8723784868812</v>
       </c>
       <c r="P21" t="n">
-        <v>180.9187551847348</v>
+        <v>180.7384918913073</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.588658208500044</v>
+        <v>1.526548378522063</v>
       </c>
       <c r="R21" t="n">
-        <v>76.11886165408519</v>
+        <v>75.77367782572891</v>
       </c>
       <c r="S21" t="n">
-        <v>15461897.2773681</v>
+        <v>16078138.33966601</v>
       </c>
       <c r="T21" t="n">
-        <v>79.30405093073888</v>
+        <v>79.16112704052912</v>
       </c>
       <c r="U21" t="n">
-        <v>24.86031760793131</v>
+        <v>24.41948883414722</v>
       </c>
       <c r="V21" t="n">
-        <v>183.1438840745184</v>
+        <v>183.4407367511715</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>64.69860750180831</v>
+        <v>64.15824666706655</v>
       </c>
       <c r="Y21" t="n">
-        <v>1074530.059269408</v>
+        <v>1029831.372285409</v>
       </c>
       <c r="Z21" t="n">
-        <v>69.90788450666525</v>
+        <v>69.70320721376621</v>
       </c>
     </row>
     <row r="22">
@@ -2005,76 +2005,76 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>25.38983957219251</v>
+        <v>25.53409090909091</v>
       </c>
       <c r="D22" t="n">
-        <v>182.8754010695187</v>
+        <v>182.8522727272727</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>66.74171122994652</v>
+        <v>67.30000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>1330446.524064171</v>
+        <v>1397642.045454545</v>
       </c>
       <c r="H22" t="n">
-        <v>70.87700534759358</v>
+        <v>71.20227272727273</v>
       </c>
       <c r="I22" t="n">
-        <v>24.90909090909091</v>
+        <v>24.86776859504132</v>
       </c>
       <c r="J22" t="n">
-        <v>184.6772727272727</v>
+        <v>184.801652892562</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>70.05</v>
+        <v>69.91735537190083</v>
       </c>
       <c r="M22" t="n">
-        <v>2789659.090909091</v>
+        <v>2747314.049586777</v>
       </c>
       <c r="N22" t="n">
-        <v>74.65909090909091</v>
+        <v>74.55371900826447</v>
       </c>
       <c r="O22" t="n">
-        <v>23.96401371066244</v>
+        <v>23.55517977618334</v>
       </c>
       <c r="P22" t="n">
-        <v>182.7557862196891</v>
+        <v>182.0915905886342</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>64.26416148906799</v>
+        <v>64.00166367709002</v>
       </c>
       <c r="S22" t="n">
-        <v>1148810.962755532</v>
+        <v>1151393.808676019</v>
       </c>
       <c r="T22" t="n">
-        <v>70.60957445485401</v>
+        <v>71.1175412293853</v>
       </c>
       <c r="U22" t="n">
-        <v>25.88763636363636</v>
+        <v>25.70307692307692</v>
       </c>
       <c r="V22" t="n">
-        <v>181.2584195804196</v>
+        <v>181.7978385251113</v>
       </c>
       <c r="W22" t="n">
-        <v>1.041741258741259</v>
+        <v>1.036020343293071</v>
       </c>
       <c r="X22" t="n">
-        <v>67.43983216783218</v>
+        <v>67.48634456452638</v>
       </c>
       <c r="Y22" t="n">
-        <v>1614444.055944056</v>
+        <v>1625925.047679593</v>
       </c>
       <c r="Z22" t="n">
-        <v>72.04871328671328</v>
+        <v>72.29641449459632</v>
       </c>
     </row>
     <row r="23">
@@ -2087,76 +2087,76 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>24.83522727272727</v>
+        <v>24.67012987012987</v>
       </c>
       <c r="D23" t="n">
-        <v>185.2846590909091</v>
+        <v>184.774025974026</v>
       </c>
       <c r="E23" t="n">
-        <v>1.048295454545455</v>
+        <v>1.068831168831169</v>
       </c>
       <c r="F23" t="n">
-        <v>70.28352272727273</v>
+        <v>69.61688311688312</v>
       </c>
       <c r="G23" t="n">
-        <v>3159488.636363637</v>
+        <v>2894285.714285714</v>
       </c>
       <c r="H23" t="n">
-        <v>75.71704545454546</v>
+        <v>75.32337662337662</v>
       </c>
       <c r="I23" t="n">
-        <v>26.07070707070707</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="J23" t="n">
-        <v>182.7424242424243</v>
+        <v>183.2363636363637</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>70.45454545454544</v>
+        <v>70.37272727272727</v>
       </c>
       <c r="M23" t="n">
-        <v>2558207.07070707</v>
+        <v>2475000</v>
       </c>
       <c r="N23" t="n">
-        <v>74.2121212121212</v>
+        <v>74.32727272727273</v>
       </c>
       <c r="O23" t="n">
-        <v>24.6143007556051</v>
+        <v>25.21638707508273</v>
       </c>
       <c r="P23" t="n">
-        <v>184.460542665366</v>
+        <v>184.593419865159</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.093067748978075</v>
+        <v>1.106499177151351</v>
       </c>
       <c r="R23" t="n">
-        <v>68.31454288213799</v>
+        <v>68.52573171594911</v>
       </c>
       <c r="S23" t="n">
-        <v>2369897.367188468</v>
+        <v>2359444.897895985</v>
       </c>
       <c r="T23" t="n">
-        <v>73.64909265452744</v>
+        <v>73.46028870485392</v>
       </c>
       <c r="U23" t="n">
-        <v>25.2253870927784</v>
+        <v>25.62051158181593</v>
       </c>
       <c r="V23" t="n">
-        <v>182.4582667533754</v>
+        <v>181.8859912671869</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>68.2916480862133</v>
+        <v>68.5828369255543</v>
       </c>
       <c r="Y23" t="n">
-        <v>1968662.929931046</v>
+        <v>2021058.55165366</v>
       </c>
       <c r="Z23" t="n">
-        <v>73.34889704364342</v>
+        <v>73.32199616003963</v>
       </c>
     </row>
     <row r="24">
@@ -2169,76 +2169,76 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>23.51336898395722</v>
+        <v>23.66022727272727</v>
       </c>
       <c r="D24" t="n">
-        <v>184.3983957219251</v>
+        <v>184.1909090909091</v>
       </c>
       <c r="E24" t="n">
-        <v>1.119786096256685</v>
+        <v>1.152272727272727</v>
       </c>
       <c r="F24" t="n">
-        <v>68.04278074866309</v>
+        <v>68.21590909090909</v>
       </c>
       <c r="G24" t="n">
-        <v>2179572.192513369</v>
+        <v>2279204.545454545</v>
       </c>
       <c r="H24" t="n">
-        <v>75.11764705882354</v>
+        <v>75.2715909090909</v>
       </c>
       <c r="I24" t="n">
-        <v>26.09488636363636</v>
+        <v>25.81904761904762</v>
       </c>
       <c r="J24" t="n">
-        <v>182.0313131313131</v>
+        <v>181.2777777777778</v>
       </c>
       <c r="K24" t="n">
-        <v>1.092550505050505</v>
+        <v>1.044444444444445</v>
       </c>
       <c r="L24" t="n">
-        <v>71.28573232323234</v>
+        <v>71.04126984126985</v>
       </c>
       <c r="M24" t="n">
-        <v>3390509.785353535</v>
+        <v>3379007.936507937</v>
       </c>
       <c r="N24" t="n">
-        <v>73.5072601010101</v>
+        <v>73.44603174603175</v>
       </c>
       <c r="O24" t="n">
-        <v>24.17799173248466</v>
+        <v>24.65211410541157</v>
       </c>
       <c r="P24" t="n">
-        <v>183.1683435468368</v>
+        <v>183.7964656070138</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.118994413451153</v>
+        <v>1.163153532624104</v>
       </c>
       <c r="R24" t="n">
-        <v>67.5497590991599</v>
+        <v>68.57053335988506</v>
       </c>
       <c r="S24" t="n">
-        <v>2264739.295663167</v>
+        <v>2403303.461797939</v>
       </c>
       <c r="T24" t="n">
-        <v>74.15072340261564</v>
+        <v>75.02834098236198</v>
       </c>
       <c r="U24" t="n">
-        <v>25.53798662278921</v>
+        <v>26.30193732193732</v>
       </c>
       <c r="V24" t="n">
-        <v>182.9264350690574</v>
+        <v>183.4291900691901</v>
       </c>
       <c r="W24" t="n">
-        <v>1.187009844257287</v>
+        <v>1.247944647944648</v>
       </c>
       <c r="X24" t="n">
-        <v>68.93913274660477</v>
+        <v>69.90273504273503</v>
       </c>
       <c r="Y24" t="n">
-        <v>2350843.943674878</v>
+        <v>2647104.029304029</v>
       </c>
       <c r="Z24" t="n">
-        <v>72.42308060436177</v>
+        <v>72.62474562474563</v>
       </c>
     </row>
     <row r="25">
@@ -2251,76 +2251,76 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>25.89946524064171</v>
+        <v>25.84431818181818</v>
       </c>
       <c r="D25" t="n">
-        <v>186.2572192513369</v>
+        <v>186.2375</v>
       </c>
       <c r="E25" t="n">
-        <v>1.275935828877006</v>
+        <v>1.235227272727273</v>
       </c>
       <c r="F25" t="n">
-        <v>75.78983957219252</v>
+        <v>76.16022727272727</v>
       </c>
       <c r="G25" t="n">
-        <v>12650855.61497326</v>
+        <v>13589204.54545454</v>
       </c>
       <c r="H25" t="n">
-        <v>79.04010695187166</v>
+        <v>79.38636363636363</v>
       </c>
       <c r="I25" t="n">
-        <v>25.96022727272727</v>
+        <v>26.32467532467533</v>
       </c>
       <c r="J25" t="n">
-        <v>182.1534090909091</v>
+        <v>182.3246753246753</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>67.96590909090909</v>
+        <v>68.09090909090909</v>
       </c>
       <c r="M25" t="n">
-        <v>1431676.136363636</v>
+        <v>1386038.961038961</v>
       </c>
       <c r="N25" t="n">
-        <v>71.3125</v>
+        <v>71.15584415584416</v>
       </c>
       <c r="O25" t="n">
-        <v>24.57152140523933</v>
+        <v>25.07500434882884</v>
       </c>
       <c r="P25" t="n">
-        <v>185.391205899366</v>
+        <v>184.7674292753385</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.16637106491948</v>
+        <v>1.219184687431591</v>
       </c>
       <c r="R25" t="n">
-        <v>72.04009418022972</v>
+        <v>72.01683930051286</v>
       </c>
       <c r="S25" t="n">
-        <v>6506192.078869222</v>
+        <v>5636406.245113675</v>
       </c>
       <c r="T25" t="n">
-        <v>76.63134153362353</v>
+        <v>75.79466071316884</v>
       </c>
       <c r="U25" t="n">
-        <v>24.20298770171053</v>
+        <v>24.05117623117623</v>
       </c>
       <c r="V25" t="n">
-        <v>181.7787160578901</v>
+        <v>182.15185999186</v>
       </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>66.87255769108531</v>
+        <v>66.85603581603581</v>
       </c>
       <c r="Y25" t="n">
-        <v>1468977.295540743</v>
+        <v>1492421.041921042</v>
       </c>
       <c r="Z25" t="n">
-        <v>72.89249775226892</v>
+        <v>72.97322751322751</v>
       </c>
     </row>
     <row r="26">
@@ -2333,76 +2333,76 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>23.85227272727273</v>
+        <v>24.10227272727273</v>
       </c>
       <c r="D26" t="n">
-        <v>184.9125</v>
+        <v>184.7272727272727</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>70.99431818181819</v>
+        <v>71.06818181818181</v>
       </c>
       <c r="G26" t="n">
-        <v>4426576.704545455</v>
+        <v>4321590.909090909</v>
       </c>
       <c r="H26" t="n">
-        <v>76.73238636363635</v>
+        <v>76.45454545454545</v>
       </c>
       <c r="I26" t="n">
-        <v>25.65738636363636</v>
+        <v>25.81298701298701</v>
       </c>
       <c r="J26" t="n">
-        <v>182.9284090909091</v>
+        <v>181.7987012987013</v>
       </c>
       <c r="K26" t="n">
-        <v>1.048863636363636</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>67.19374999999999</v>
+        <v>67.54415584415585</v>
       </c>
       <c r="M26" t="n">
-        <v>1440724.431818182</v>
+        <v>1533863.636363636</v>
       </c>
       <c r="N26" t="n">
-        <v>71.80397727272727</v>
+        <v>71.94415584415584</v>
       </c>
       <c r="O26" t="n">
-        <v>23.24593971797401</v>
+        <v>23.19467686999546</v>
       </c>
       <c r="P26" t="n">
-        <v>184.4125499888806</v>
+        <v>184.6840424242036</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>67.91933814500578</v>
+        <v>67.5394128219981</v>
       </c>
       <c r="S26" t="n">
-        <v>2648315.453954744</v>
+        <v>2556680.846396925</v>
       </c>
       <c r="T26" t="n">
-        <v>75.05871282201821</v>
+        <v>74.71708972995049</v>
       </c>
       <c r="U26" t="n">
-        <v>26.64023610899969</v>
+        <v>26.58976060976061</v>
       </c>
       <c r="V26" t="n">
-        <v>181.6456480214632</v>
+        <v>181.9976401376401</v>
       </c>
       <c r="W26" t="n">
-        <v>1.136952686001599</v>
+        <v>1.114663114663115</v>
       </c>
       <c r="X26" t="n">
-        <v>66.7535016307163</v>
+        <v>66.7907018907019</v>
       </c>
       <c r="Y26" t="n">
-        <v>1326626.642698586</v>
+        <v>1349302.142302142</v>
       </c>
       <c r="Z26" t="n">
-        <v>70.54761178887537</v>
+        <v>70.48701964701965</v>
       </c>
     </row>
     <row r="27">
@@ -2415,76 +2415,76 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>26.2530303030303</v>
+        <v>25.72537878787879</v>
       </c>
       <c r="D27" t="n">
-        <v>184.3292929292929</v>
+        <v>185.1551767676768</v>
       </c>
       <c r="E27" t="n">
-        <v>1.41155303030303</v>
+        <v>1.326515151515151</v>
       </c>
       <c r="F27" t="n">
-        <v>72.08440656565656</v>
+        <v>71.22108585858585</v>
       </c>
       <c r="G27" t="n">
-        <v>3591829.22979798</v>
+        <v>3141243.686868687</v>
       </c>
       <c r="H27" t="n">
-        <v>76.73301767676767</v>
+        <v>76.6205808080808</v>
       </c>
       <c r="I27" t="n">
-        <v>26.04895833333333</v>
+        <v>25.89047619047619</v>
       </c>
       <c r="J27" t="n">
-        <v>183.3173611111111</v>
+        <v>183.2238095238095</v>
       </c>
       <c r="K27" t="n">
-        <v>1.107986111111111</v>
+        <v>1.104761904761905</v>
       </c>
       <c r="L27" t="n">
-        <v>68.32361111111112</v>
+        <v>68.51904761904761</v>
       </c>
       <c r="M27" t="n">
-        <v>1612200.520833333</v>
+        <v>1678769.841269841</v>
       </c>
       <c r="N27" t="n">
-        <v>72.12708333333333</v>
+        <v>72.43333333333334</v>
       </c>
       <c r="O27" t="n">
-        <v>24.9311284544162</v>
+        <v>24.82486140880104</v>
       </c>
       <c r="P27" t="n">
-        <v>184.1562631711357</v>
+        <v>183.8016459937551</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.22161293970963</v>
+        <v>1.210687961419386</v>
       </c>
       <c r="R27" t="n">
-        <v>70.43439926510482</v>
+        <v>69.95947136884443</v>
       </c>
       <c r="S27" t="n">
-        <v>3692779.612421285</v>
+        <v>3162273.132161097</v>
       </c>
       <c r="T27" t="n">
-        <v>75.88315246645284</v>
+        <v>75.82969602550872</v>
       </c>
       <c r="U27" t="n">
-        <v>24.06148563210563</v>
+        <v>23.94467120181406</v>
       </c>
       <c r="V27" t="n">
-        <v>183.7574836970969</v>
+        <v>184.4581349206349</v>
       </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>64.34535148497892</v>
+        <v>64.31975623582767</v>
       </c>
       <c r="Y27" t="n">
-        <v>1158894.516700286</v>
+        <v>1139713.860544218</v>
       </c>
       <c r="Z27" t="n">
-        <v>70.7957318181199</v>
+        <v>70.93358843537415</v>
       </c>
     </row>
     <row r="28">
@@ -2497,76 +2497,76 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>25.38983957219251</v>
+        <v>25.53409090909091</v>
       </c>
       <c r="D28" t="n">
-        <v>182.8754010695187</v>
+        <v>182.8522727272727</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>66.74171122994652</v>
+        <v>67.30000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>1330446.524064171</v>
+        <v>1397642.045454545</v>
       </c>
       <c r="H28" t="n">
-        <v>70.87700534759358</v>
+        <v>71.20227272727273</v>
       </c>
       <c r="I28" t="n">
-        <v>26.07070707070707</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="J28" t="n">
-        <v>182.7424242424243</v>
+        <v>183.2363636363637</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>70.45454545454544</v>
+        <v>70.37272727272727</v>
       </c>
       <c r="M28" t="n">
-        <v>2558207.07070707</v>
+        <v>2475000</v>
       </c>
       <c r="N28" t="n">
-        <v>74.2121212121212</v>
+        <v>74.32727272727273</v>
       </c>
       <c r="O28" t="n">
-        <v>23.96401371066244</v>
+        <v>23.55517977618334</v>
       </c>
       <c r="P28" t="n">
-        <v>182.7557862196891</v>
+        <v>182.0915905886342</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>64.26416148906799</v>
+        <v>64.00166367709002</v>
       </c>
       <c r="S28" t="n">
-        <v>1148810.962755532</v>
+        <v>1151393.808676019</v>
       </c>
       <c r="T28" t="n">
-        <v>70.60957445485401</v>
+        <v>71.1175412293853</v>
       </c>
       <c r="U28" t="n">
-        <v>25.2253870927784</v>
+        <v>25.62051158181593</v>
       </c>
       <c r="V28" t="n">
-        <v>182.4582667533754</v>
+        <v>181.8859912671869</v>
       </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>68.2916480862133</v>
+        <v>68.5828369255543</v>
       </c>
       <c r="Y28" t="n">
-        <v>1968662.929931046</v>
+        <v>2021058.55165366</v>
       </c>
       <c r="Z28" t="n">
-        <v>73.34889704364342</v>
+        <v>73.32199616003963</v>
       </c>
     </row>
     <row r="29">
@@ -2579,22 +2579,22 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>27.7473559120618</v>
+        <v>27.89450056116723</v>
       </c>
       <c r="D29" t="n">
-        <v>181.5882947118241</v>
+        <v>180.9455667789001</v>
       </c>
       <c r="E29" t="n">
-        <v>1.034224598930481</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>67.67801544860369</v>
+        <v>67.60897867564535</v>
       </c>
       <c r="G29" t="n">
-        <v>1467750</v>
+        <v>1260000</v>
       </c>
       <c r="H29" t="n">
-        <v>70.06494355317885</v>
+        <v>69.80953984287318</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -2603,22 +2603,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>25.55223640831731</v>
+        <v>25.19443532313097</v>
       </c>
       <c r="P29" t="n">
-        <v>178.8410642175611</v>
+        <v>178.4018239248674</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.036833661694343</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>65.21807424818194</v>
+        <v>65.03192696192696</v>
       </c>
       <c r="S29" t="n">
-        <v>1219814.486476529</v>
+        <v>1260961.610129001</v>
       </c>
       <c r="T29" t="n">
-        <v>69.39089863136371</v>
+        <v>69.59661227661228</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2637,76 +2637,76 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>25.65738636363636</v>
+        <v>25.81298701298701</v>
       </c>
       <c r="D30" t="n">
-        <v>182.9284090909091</v>
+        <v>181.7987012987013</v>
       </c>
       <c r="E30" t="n">
-        <v>1.048863636363636</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>67.19374999999999</v>
+        <v>67.54415584415585</v>
       </c>
       <c r="G30" t="n">
-        <v>1440724.431818182</v>
+        <v>1533863.636363636</v>
       </c>
       <c r="H30" t="n">
-        <v>71.80397727272727</v>
+        <v>71.94415584415584</v>
       </c>
       <c r="I30" t="n">
-        <v>26.04895833333333</v>
+        <v>25.89047619047619</v>
       </c>
       <c r="J30" t="n">
-        <v>183.3173611111111</v>
+        <v>183.2238095238095</v>
       </c>
       <c r="K30" t="n">
-        <v>1.107986111111111</v>
+        <v>1.104761904761905</v>
       </c>
       <c r="L30" t="n">
-        <v>68.32361111111112</v>
+        <v>68.51904761904761</v>
       </c>
       <c r="M30" t="n">
-        <v>1612200.520833333</v>
+        <v>1678769.841269841</v>
       </c>
       <c r="N30" t="n">
-        <v>72.12708333333333</v>
+        <v>72.43333333333334</v>
       </c>
       <c r="O30" t="n">
-        <v>26.64023610899969</v>
+        <v>26.58976060976061</v>
       </c>
       <c r="P30" t="n">
-        <v>181.6456480214632</v>
+        <v>181.9976401376401</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.136952686001599</v>
+        <v>1.114663114663115</v>
       </c>
       <c r="R30" t="n">
-        <v>66.7535016307163</v>
+        <v>66.7907018907019</v>
       </c>
       <c r="S30" t="n">
-        <v>1326626.642698586</v>
+        <v>1349302.142302142</v>
       </c>
       <c r="T30" t="n">
-        <v>70.54761178887537</v>
+        <v>70.48701964701965</v>
       </c>
       <c r="U30" t="n">
-        <v>24.06148563210563</v>
+        <v>23.94467120181406</v>
       </c>
       <c r="V30" t="n">
-        <v>183.7574836970969</v>
+        <v>184.4581349206349</v>
       </c>
       <c r="W30" t="n">
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>64.34535148497892</v>
+        <v>64.31975623582767</v>
       </c>
       <c r="Y30" t="n">
-        <v>1158894.516700286</v>
+        <v>1139713.860544218</v>
       </c>
       <c r="Z30" t="n">
-        <v>70.7957318181199</v>
+        <v>70.93358843537415</v>
       </c>
     </row>
     <row r="31">
@@ -2719,76 +2719,76 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>26.2530303030303</v>
+        <v>25.72537878787879</v>
       </c>
       <c r="D31" t="n">
-        <v>184.3292929292929</v>
+        <v>185.1551767676768</v>
       </c>
       <c r="E31" t="n">
-        <v>1.41155303030303</v>
+        <v>1.326515151515151</v>
       </c>
       <c r="F31" t="n">
-        <v>72.08440656565656</v>
+        <v>71.22108585858585</v>
       </c>
       <c r="G31" t="n">
-        <v>3591829.22979798</v>
+        <v>3141243.686868687</v>
       </c>
       <c r="H31" t="n">
-        <v>76.73301767676767</v>
+        <v>76.6205808080808</v>
       </c>
       <c r="I31" t="n">
-        <v>26.12897727272728</v>
+        <v>25.44285714285714</v>
       </c>
       <c r="J31" t="n">
-        <v>184.0391414141414</v>
+        <v>183.563492063492</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>66.85138888888889</v>
+        <v>66.64603174603175</v>
       </c>
       <c r="M31" t="n">
-        <v>1185452.967171717</v>
+        <v>1211587.301587302</v>
       </c>
       <c r="N31" t="n">
-        <v>69.99785353535353</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="O31" t="n">
-        <v>24.9311284544162</v>
+        <v>24.82486140880104</v>
       </c>
       <c r="P31" t="n">
-        <v>184.1562631711357</v>
+        <v>183.8016459937551</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.22161293970963</v>
+        <v>1.210687961419386</v>
       </c>
       <c r="R31" t="n">
-        <v>70.43439926510482</v>
+        <v>69.95947136884443</v>
       </c>
       <c r="S31" t="n">
-        <v>3692779.612421285</v>
+        <v>3162273.132161097</v>
       </c>
       <c r="T31" t="n">
-        <v>75.88315246645284</v>
+        <v>75.82969602550872</v>
       </c>
       <c r="U31" t="n">
-        <v>24.87265791575574</v>
+        <v>24.89280560709132</v>
       </c>
       <c r="V31" t="n">
-        <v>183.4896629849619</v>
+        <v>183.361605854463</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>64.88296396990691</v>
+        <v>64.58005875077303</v>
       </c>
       <c r="Y31" t="n">
-        <v>1058988.863883701</v>
+        <v>1031453.133374562</v>
       </c>
       <c r="Z31" t="n">
-        <v>69.34134413593652</v>
+        <v>69.26774582560297</v>
       </c>
     </row>
     <row r="32">
@@ -2801,76 +2801,76 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>28.85</v>
+        <v>28.87142857142857</v>
       </c>
       <c r="D32" t="n">
-        <v>183.7528409090909</v>
+        <v>183.4142857142857</v>
       </c>
       <c r="E32" t="n">
-        <v>1.147727272727273</v>
+        <v>1.157142857142857</v>
       </c>
       <c r="F32" t="n">
-        <v>67.9153409090909</v>
+        <v>67.78571428571429</v>
       </c>
       <c r="G32" t="n">
-        <v>1070465.909090909</v>
+        <v>1045500</v>
       </c>
       <c r="H32" t="n">
-        <v>70.03011363636364</v>
+        <v>69.98571428571428</v>
       </c>
       <c r="I32" t="n">
-        <v>25.72727272727273</v>
+        <v>26.41558441558441</v>
       </c>
       <c r="J32" t="n">
-        <v>184.2102272727273</v>
+        <v>184.3896103896104</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>66.59090909090909</v>
+        <v>67.1948051948052</v>
       </c>
       <c r="M32" t="n">
-        <v>1288068.181818182</v>
+        <v>1326623.376623377</v>
       </c>
       <c r="N32" t="n">
-        <v>70.38636363636363</v>
+        <v>70.55844155844156</v>
       </c>
       <c r="O32" t="n">
-        <v>25.20870246299594</v>
+        <v>25.22084760994699</v>
       </c>
       <c r="P32" t="n">
-        <v>184.9972915610959</v>
+        <v>185.1004652191609</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.045622275771732</v>
+        <v>1.035889359088117</v>
       </c>
       <c r="R32" t="n">
-        <v>65.18824455536412</v>
+        <v>65.26384562297606</v>
       </c>
       <c r="S32" t="n">
-        <v>987446.7169027631</v>
+        <v>999487.5229727715</v>
       </c>
       <c r="T32" t="n">
-        <v>68.72725022964153</v>
+        <v>68.73200984890426</v>
       </c>
       <c r="U32" t="n">
-        <v>24.86031760793131</v>
+        <v>24.41948883414722</v>
       </c>
       <c r="V32" t="n">
-        <v>183.1438840745184</v>
+        <v>183.4407367511715</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>64.69860750180831</v>
+        <v>64.15824666706655</v>
       </c>
       <c r="Y32" t="n">
-        <v>1074530.059269408</v>
+        <v>1029831.372285409</v>
       </c>
       <c r="Z32" t="n">
-        <v>69.90788450666525</v>
+        <v>69.70320721376621</v>
       </c>
     </row>
     <row r="33">
@@ -2883,76 +2883,76 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>26.84976076555024</v>
+        <v>26.86</v>
       </c>
       <c r="D33" t="n">
-        <v>181.4129186602871</v>
+        <v>181.6572727272727</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>67.53779904306221</v>
+        <v>67.4309090909091</v>
       </c>
       <c r="G33" t="n">
-        <v>1317033.492822966</v>
+        <v>1277590.909090909</v>
       </c>
       <c r="H33" t="n">
-        <v>70.63827751196173</v>
+        <v>70.28545454545454</v>
       </c>
       <c r="I33" t="n">
-        <v>25.55026737967914</v>
+        <v>25.74204545454545</v>
       </c>
       <c r="J33" t="n">
-        <v>186.6604278074867</v>
+        <v>186.9363636363636</v>
       </c>
       <c r="K33" t="n">
-        <v>1.187700534759358</v>
+        <v>1.214772727272727</v>
       </c>
       <c r="L33" t="n">
-        <v>73.5529411764706</v>
+        <v>73.25</v>
       </c>
       <c r="M33" t="n">
-        <v>5926871.657754011</v>
+        <v>5306079.545454546</v>
       </c>
       <c r="N33" t="n">
-        <v>77.51925133689839</v>
+        <v>77.25454545454545</v>
       </c>
       <c r="O33" t="n">
-        <v>25.28923867216773</v>
+        <v>25.63088518888519</v>
       </c>
       <c r="P33" t="n">
-        <v>179.4360243633813</v>
+        <v>179.4868835053835</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>66.08823967540215</v>
+        <v>66.03421056721056</v>
       </c>
       <c r="S33" t="n">
-        <v>1242947.921008562</v>
+        <v>1188850.593850594</v>
       </c>
       <c r="T33" t="n">
-        <v>71.20271346671805</v>
+        <v>70.69366881266882</v>
       </c>
       <c r="U33" t="n">
-        <v>24.50582693175426</v>
+        <v>24.18748135890846</v>
       </c>
       <c r="V33" t="n">
-        <v>184.9363906840302</v>
+        <v>185.0565917079616</v>
       </c>
       <c r="W33" t="n">
-        <v>1.145053993867822</v>
+        <v>1.13142152900961</v>
       </c>
       <c r="X33" t="n">
-        <v>71.03316229230067</v>
+        <v>70.81202993245441</v>
       </c>
       <c r="Y33" t="n">
-        <v>4184631.048136781</v>
+        <v>3964935.51087704</v>
       </c>
       <c r="Z33" t="n">
-        <v>77.17398527429526</v>
+        <v>77.16509865602913</v>
       </c>
     </row>
     <row r="34">
@@ -2997,76 +2997,76 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>25.96022727272727</v>
+        <v>26.32467532467533</v>
       </c>
       <c r="D35" t="n">
-        <v>182.1534090909091</v>
+        <v>182.3246753246753</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>67.96590909090909</v>
+        <v>68.09090909090909</v>
       </c>
       <c r="G35" t="n">
-        <v>1431676.136363636</v>
+        <v>1386038.961038961</v>
       </c>
       <c r="H35" t="n">
-        <v>71.3125</v>
+        <v>71.15584415584416</v>
       </c>
       <c r="I35" t="n">
-        <v>26.82929292929293</v>
+        <v>26.78567493112947</v>
       </c>
       <c r="J35" t="n">
-        <v>185.6604545454546</v>
+        <v>185.6598714416896</v>
       </c>
       <c r="K35" t="n">
-        <v>1.075909090909091</v>
+        <v>1.085123966942149</v>
       </c>
       <c r="L35" t="n">
-        <v>69.71712121212121</v>
+        <v>69.30918273645547</v>
       </c>
       <c r="M35" t="n">
-        <v>2019979.797979798</v>
+        <v>1959320.477502296</v>
       </c>
       <c r="N35" t="n">
-        <v>73.00373737373738</v>
+        <v>72.65656565656565</v>
       </c>
       <c r="O35" t="n">
-        <v>24.20298770171053</v>
+        <v>24.05117623117623</v>
       </c>
       <c r="P35" t="n">
-        <v>181.7787160578901</v>
+        <v>182.15185999186</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>66.87255769108531</v>
+        <v>66.85603581603581</v>
       </c>
       <c r="S35" t="n">
-        <v>1468977.295540743</v>
+        <v>1492421.041921042</v>
       </c>
       <c r="T35" t="n">
-        <v>72.89249775226892</v>
+        <v>72.97322751322751</v>
       </c>
       <c r="U35" t="n">
-        <v>26.98757034632035</v>
+        <v>27.35946734424995</v>
       </c>
       <c r="V35" t="n">
-        <v>185.3590241624318</v>
+        <v>185.3063988843831</v>
       </c>
       <c r="W35" t="n">
-        <v>1.133275574063617</v>
+        <v>1.12314477354003</v>
       </c>
       <c r="X35" t="n">
-        <v>69.62046988518728</v>
+        <v>70.03460688191913</v>
       </c>
       <c r="Y35" t="n">
-        <v>2075383.015716168</v>
+        <v>2126572.170747566</v>
       </c>
       <c r="Z35" t="n">
-        <v>73.06944939299831</v>
+        <v>73.13433396642883</v>
       </c>
     </row>
     <row r="36">
@@ -3079,76 +3079,76 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>23.85227272727273</v>
+        <v>24.10227272727273</v>
       </c>
       <c r="D36" t="n">
-        <v>184.9125</v>
+        <v>184.7272727272727</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>70.99431818181819</v>
+        <v>71.06818181818181</v>
       </c>
       <c r="G36" t="n">
-        <v>4426576.704545455</v>
+        <v>4321590.909090909</v>
       </c>
       <c r="H36" t="n">
-        <v>76.73238636363635</v>
+        <v>76.45454545454545</v>
       </c>
       <c r="I36" t="n">
-        <v>23.51336898395722</v>
+        <v>23.66022727272727</v>
       </c>
       <c r="J36" t="n">
-        <v>184.3983957219251</v>
+        <v>184.1909090909091</v>
       </c>
       <c r="K36" t="n">
-        <v>1.119786096256685</v>
+        <v>1.152272727272727</v>
       </c>
       <c r="L36" t="n">
-        <v>68.04278074866309</v>
+        <v>68.21590909090909</v>
       </c>
       <c r="M36" t="n">
-        <v>2179572.192513369</v>
+        <v>2279204.545454545</v>
       </c>
       <c r="N36" t="n">
-        <v>75.11764705882354</v>
+        <v>75.2715909090909</v>
       </c>
       <c r="O36" t="n">
-        <v>23.24593971797401</v>
+        <v>23.19467686999546</v>
       </c>
       <c r="P36" t="n">
-        <v>184.4125499888806</v>
+        <v>184.6840424242036</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>67.91933814500578</v>
+        <v>67.5394128219981</v>
       </c>
       <c r="S36" t="n">
-        <v>2648315.453954744</v>
+        <v>2556680.846396925</v>
       </c>
       <c r="T36" t="n">
-        <v>75.05871282201821</v>
+        <v>74.71708972995049</v>
       </c>
       <c r="U36" t="n">
-        <v>24.17799173248466</v>
+        <v>24.65211410541157</v>
       </c>
       <c r="V36" t="n">
-        <v>183.1683435468368</v>
+        <v>183.7964656070138</v>
       </c>
       <c r="W36" t="n">
-        <v>1.118994413451153</v>
+        <v>1.163153532624104</v>
       </c>
       <c r="X36" t="n">
-        <v>67.5497590991599</v>
+        <v>68.57053335988506</v>
       </c>
       <c r="Y36" t="n">
-        <v>2264739.295663167</v>
+        <v>2403303.461797939</v>
       </c>
       <c r="Z36" t="n">
-        <v>74.15072340261564</v>
+        <v>75.02834098236198</v>
       </c>
     </row>
     <row r="37">
@@ -3161,22 +3161,22 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>26.04772727272727</v>
+        <v>26.08051948051948</v>
       </c>
       <c r="D37" t="n">
-        <v>184.8403409090909</v>
+        <v>184.2207792207792</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>65.97727272727273</v>
+        <v>65.64805194805194</v>
       </c>
       <c r="G37" t="n">
-        <v>1178267.045454545</v>
+        <v>1164110.389610389</v>
       </c>
       <c r="H37" t="n">
-        <v>69.29375</v>
+        <v>68.99999999999999</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -3185,22 +3185,22 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>26.03236695621207</v>
+        <v>26.15596963423051</v>
       </c>
       <c r="P37" t="n">
-        <v>182.606010776663</v>
+        <v>182.3768115942029</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>64.42874415489905</v>
+        <v>64.2716816195077</v>
       </c>
       <c r="S37" t="n">
-        <v>1062892.325305029</v>
+        <v>1000485.480702872</v>
       </c>
       <c r="T37" t="n">
-        <v>68.1845579013378</v>
+        <v>67.93227867140909</v>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
